--- a/backend/excel/catalogo.xlsx
+++ b/backend/excel/catalogo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939" firstSheet="1" activeTab="11"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10275" tabRatio="939"/>
   </bookViews>
   <sheets>
     <sheet name="VENTANAS_HERRERO" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="280">
   <si>
     <t>MEDIDA</t>
   </si>
@@ -817,9 +817,6 @@
   </si>
   <si>
     <t>SIMIL MADERA</t>
-  </si>
-  <si>
-    <t>2.8</t>
   </si>
   <si>
     <t>GRANERO</t>
@@ -1257,7 +1254,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>22500</v>
+        <v>23500</v>
       </c>
       <c r="C2" s="1">
         <v>7179</v>
@@ -1266,7 +1263,7 @@
         <v>9659</v>
       </c>
       <c r="E2" s="1">
-        <v>2709</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1283,7 +1280,7 @@
         <v>10839</v>
       </c>
       <c r="E3" s="1">
-        <v>3784</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1300,7 +1297,7 @@
         <v>12428</v>
       </c>
       <c r="E4" s="1">
-        <v>4865</v>
+        <v>5106</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1317,7 +1314,7 @@
         <v>14016</v>
       </c>
       <c r="E5" s="1">
-        <v>5959</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1334,7 +1331,7 @@
         <v>16399</v>
       </c>
       <c r="E6" s="1">
-        <v>7568</v>
+        <v>7943</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1351,7 +1348,7 @@
         <v>18781</v>
       </c>
       <c r="E7" s="1">
-        <v>9197</v>
+        <v>9652</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1368,7 +1365,7 @@
         <v>20370</v>
       </c>
       <c r="E8" s="1">
-        <v>10278</v>
+        <v>10787</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1385,7 +1382,7 @@
         <v>12194</v>
       </c>
       <c r="E9" s="1">
-        <v>4509</v>
+        <v>4733</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1402,7 +1399,7 @@
         <v>14016</v>
       </c>
       <c r="E10" s="1">
-        <v>6309</v>
+        <v>6622</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1419,7 +1416,7 @@
         <v>15838</v>
       </c>
       <c r="E11" s="1">
-        <v>8115</v>
+        <v>8517</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1436,7 +1433,7 @@
         <v>17660</v>
       </c>
       <c r="E12" s="1">
-        <v>9915</v>
+        <v>10406</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1453,7 +1450,7 @@
         <v>20393</v>
       </c>
       <c r="E13" s="1">
-        <v>12625</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1470,7 +1467,7 @@
         <v>23126</v>
       </c>
       <c r="E14" s="1">
-        <v>15328</v>
+        <v>16087</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1487,7 +1484,7 @@
         <v>24948</v>
       </c>
       <c r="E15" s="1">
-        <v>17127</v>
+        <v>17976</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1504,7 +1501,7 @@
         <v>19249</v>
       </c>
       <c r="E16" s="1">
-        <v>11359</v>
+        <v>11922</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1521,7 +1518,7 @@
         <v>21304</v>
       </c>
       <c r="E17" s="1">
-        <v>13884</v>
+        <v>14572</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1538,7 +1535,7 @@
         <v>24388</v>
       </c>
       <c r="E18" s="1">
-        <v>17668</v>
+        <v>18543</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1555,7 +1552,7 @@
         <v>27471</v>
       </c>
       <c r="E19" s="1">
-        <v>21459</v>
+        <v>22521</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1572,7 +1569,7 @@
         <v>29527</v>
       </c>
       <c r="E20" s="1">
-        <v>23977</v>
+        <v>25165</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1589,7 +1586,7 @@
         <v>22659</v>
       </c>
       <c r="E21" s="1">
-        <v>14603</v>
+        <v>15326</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1606,7 +1603,7 @@
         <v>24948</v>
       </c>
       <c r="E22" s="1">
-        <v>17853</v>
+        <v>18737</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1623,7 +1620,7 @@
         <v>28382</v>
       </c>
       <c r="E23" s="1">
-        <v>22718</v>
+        <v>23843</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1640,7 +1637,7 @@
         <v>31816</v>
       </c>
       <c r="E24" s="1">
-        <v>27583</v>
+        <v>28949</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1657,7 +1654,7 @@
         <v>34106</v>
       </c>
       <c r="E25" s="1">
-        <v>30833</v>
+        <v>32360</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1674,7 +1671,7 @@
         <v>36395</v>
       </c>
       <c r="E26" s="1">
-        <v>34077</v>
+        <v>35765</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1691,7 +1688,7 @@
         <v>38684</v>
       </c>
       <c r="E27" s="1">
-        <v>37320</v>
+        <v>39169</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1708,7 +1705,7 @@
         <v>24364</v>
       </c>
       <c r="E28" s="1">
-        <v>16231</v>
+        <v>17035</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1725,7 +1722,7 @@
         <v>26771</v>
       </c>
       <c r="E29" s="1">
-        <v>19830</v>
+        <v>20813</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1742,7 +1739,7 @@
         <v>30380</v>
       </c>
       <c r="E30" s="1">
-        <v>25243</v>
+        <v>26493</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1759,7 +1756,7 @@
         <v>33989</v>
       </c>
       <c r="E31" s="1">
-        <v>30655</v>
+        <v>32174</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1776,7 +1773,7 @@
         <v>41207</v>
       </c>
       <c r="E32" s="1">
-        <v>37861</v>
+        <v>39736</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1793,7 +1790,7 @@
         <v>41207</v>
       </c>
       <c r="E33" s="1">
-        <v>41467</v>
+        <v>43521</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1810,7 +1807,7 @@
         <v>26070</v>
       </c>
       <c r="E34" s="1">
-        <v>17853</v>
+        <v>18737</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1827,7 +1824,7 @@
         <v>28593</v>
       </c>
       <c r="E35" s="1">
-        <v>21815</v>
+        <v>22895</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1844,7 +1841,7 @@
         <v>32377</v>
       </c>
       <c r="E36" s="1">
-        <v>27768</v>
+        <v>29143</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1861,7 +1858,7 @@
         <v>36161</v>
       </c>
       <c r="E37" s="1">
-        <v>33714</v>
+        <v>35384</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1878,7 +1875,7 @@
         <v>38684</v>
       </c>
       <c r="E38" s="1">
-        <v>37683</v>
+        <v>39549</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1895,7 +1892,7 @@
         <v>41207</v>
       </c>
       <c r="E39" s="1">
-        <v>41652</v>
+        <v>43715</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1912,7 +1909,7 @@
         <v>43730</v>
       </c>
       <c r="E40" s="1">
-        <v>45620</v>
+        <v>47880</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1929,7 +1926,7 @@
         <v>31186</v>
       </c>
       <c r="E41" s="1">
-        <v>22718</v>
+        <v>23843</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1946,7 +1943,7 @@
         <v>34059</v>
       </c>
       <c r="E42" s="1">
-        <v>27768</v>
+        <v>29143</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1963,7 +1960,7 @@
         <v>38369</v>
       </c>
       <c r="E43" s="1">
-        <v>35336</v>
+        <v>37086</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1980,7 +1977,7 @@
         <v>42679</v>
       </c>
       <c r="E44" s="1">
-        <v>42911</v>
+        <v>45036</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1997,7 +1994,7 @@
         <v>45552</v>
       </c>
       <c r="E45" s="1">
-        <v>47961</v>
+        <v>50336</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2014,7 +2011,7 @@
         <v>48425</v>
       </c>
       <c r="E46" s="1">
-        <v>53004</v>
+        <v>55629</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2031,7 +2028,7 @@
         <v>51299</v>
       </c>
       <c r="E47" s="1">
-        <v>58060</v>
+        <v>60936</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2048,7 +2045,7 @@
         <v>39712</v>
       </c>
       <c r="E48" s="1">
-        <v>30833</v>
+        <v>32360</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2065,7 +2062,7 @@
         <v>43169</v>
       </c>
       <c r="E49" s="1">
-        <v>37683</v>
+        <v>39549</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2082,7 +2079,7 @@
         <v>48355</v>
       </c>
       <c r="E50" s="1">
-        <v>50486</v>
+        <v>52986</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2099,7 +2096,7 @@
         <v>53541</v>
       </c>
       <c r="E51" s="1">
-        <v>61304</v>
+        <v>64340</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2116,7 +2113,7 @@
         <v>56998</v>
       </c>
       <c r="E52" s="1">
-        <v>68516</v>
+        <v>71910</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2133,7 +2130,7 @@
         <v>60456</v>
       </c>
       <c r="E53" s="1">
-        <v>75729</v>
+        <v>79479</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2150,7 +2147,7 @@
         <v>63913</v>
       </c>
       <c r="E54" s="1">
-        <v>82941</v>
+        <v>87049</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2171,7 +2168,7 @@
       </c>
       <c r="E55" s="2">
         <f>E54*(1.05)</f>
-        <v>87088.05</v>
+        <v>91401.45</v>
       </c>
     </row>
   </sheetData>
@@ -2213,16 +2210,16 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>144222</v>
+        <v>149336</v>
       </c>
       <c r="D2">
-        <v>16398</v>
+        <v>61992</v>
       </c>
       <c r="E2">
-        <v>52409</v>
+        <v>17255</v>
       </c>
       <c r="F2">
-        <v>61992</v>
+        <v>55147</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2233,16 +2230,16 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>154959</v>
+        <v>160454</v>
       </c>
       <c r="D3">
-        <v>18920</v>
+        <v>69741</v>
       </c>
       <c r="E3">
-        <v>63231</v>
+        <v>19909</v>
       </c>
       <c r="F3">
-        <v>69741</v>
+        <v>66535</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2253,16 +2250,16 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>164244</v>
+        <v>170068</v>
       </c>
       <c r="D4">
-        <v>23185</v>
+        <v>77490</v>
       </c>
       <c r="E4">
-        <v>77460</v>
+        <v>24396</v>
       </c>
       <c r="F4">
-        <v>77490</v>
+        <v>81507</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2273,16 +2270,16 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>170596</v>
+        <v>176645</v>
       </c>
       <c r="D5">
-        <v>26030</v>
+        <v>82656</v>
       </c>
       <c r="E5">
-        <v>86942</v>
+        <v>27391</v>
       </c>
       <c r="F5">
-        <v>82656</v>
+        <v>91485</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2293,16 +2290,16 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>152076</v>
+        <v>157468</v>
       </c>
       <c r="D6">
-        <v>17280</v>
+        <v>67158</v>
       </c>
       <c r="E6">
-        <v>57370</v>
+        <v>18183</v>
       </c>
       <c r="F6">
-        <v>67158</v>
+        <v>60367</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2313,16 +2310,16 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>158569</v>
+        <v>164192</v>
       </c>
       <c r="D7">
-        <v>21070</v>
+        <v>72324</v>
       </c>
       <c r="E7">
-        <v>70012</v>
+        <v>22171</v>
       </c>
       <c r="F7">
-        <v>72324</v>
+        <v>73670</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2333,16 +2330,16 @@
         <v>21</v>
       </c>
       <c r="C8">
-        <v>169835</v>
+        <v>175857</v>
       </c>
       <c r="D8">
-        <v>25541</v>
+        <v>80073</v>
       </c>
       <c r="E8">
-        <v>85362</v>
+        <v>26876</v>
       </c>
       <c r="F8">
-        <v>80073</v>
+        <v>89822</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2353,16 +2350,16 @@
         <v>22</v>
       </c>
       <c r="C9">
-        <v>179119</v>
+        <v>185471</v>
       </c>
       <c r="D9">
-        <v>31219</v>
+        <v>87822</v>
       </c>
       <c r="E9">
-        <v>104299</v>
+        <v>32850</v>
       </c>
       <c r="F9">
-        <v>87822</v>
+        <v>109749</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2373,16 +2370,16 @@
         <v>23</v>
       </c>
       <c r="C10">
-        <v>185471</v>
+        <v>192048</v>
       </c>
       <c r="D10">
-        <v>35008</v>
+        <v>92988</v>
       </c>
       <c r="E10">
-        <v>116948</v>
+        <v>36837</v>
       </c>
       <c r="F10">
-        <v>92988</v>
+        <v>123058</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2393,16 +2390,16 @@
         <v>24</v>
       </c>
       <c r="C11">
-        <v>166951</v>
+        <v>172871</v>
       </c>
       <c r="D11">
-        <v>21083</v>
+        <v>77490</v>
       </c>
       <c r="E11">
-        <v>68781</v>
+        <v>22185</v>
       </c>
       <c r="F11">
-        <v>77490</v>
+        <v>72375</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2413,16 +2410,16 @@
         <v>25</v>
       </c>
       <c r="C12">
-        <v>173444</v>
+        <v>179595</v>
       </c>
       <c r="D12">
-        <v>25817</v>
+        <v>82656</v>
       </c>
       <c r="E12">
-        <v>79002</v>
+        <v>27166</v>
       </c>
       <c r="F12">
-        <v>82656</v>
+        <v>83129</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2433,16 +2430,16 @@
         <v>26</v>
       </c>
       <c r="C13">
-        <v>184710</v>
+        <v>191260</v>
       </c>
       <c r="D13">
-        <v>32163</v>
+        <v>90405</v>
       </c>
       <c r="E13">
-        <v>93263</v>
+        <v>33843</v>
       </c>
       <c r="F13">
-        <v>90405</v>
+        <v>98136</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2453,16 +2450,16 @@
         <v>27</v>
       </c>
       <c r="C14">
-        <v>191175</v>
+        <v>197954</v>
       </c>
       <c r="D14">
-        <v>39259</v>
+        <v>98154</v>
       </c>
       <c r="E14">
-        <v>119176</v>
+        <v>41311</v>
       </c>
       <c r="F14">
-        <v>98154</v>
+        <v>125403</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2473,16 +2470,16 @@
         <v>28</v>
       </c>
       <c r="C15">
-        <v>200347</v>
+        <v>207451</v>
       </c>
       <c r="D15">
-        <v>43993</v>
+        <v>103320</v>
       </c>
       <c r="E15">
-        <v>131326</v>
+        <v>46291</v>
       </c>
       <c r="F15">
-        <v>103320</v>
+        <v>138188</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2493,16 +2490,16 @@
         <v>31</v>
       </c>
       <c r="C16">
-        <v>174777</v>
+        <v>180974</v>
       </c>
       <c r="D16">
-        <v>23454</v>
+        <v>82656</v>
       </c>
       <c r="E16">
-        <v>83529</v>
+        <v>24679</v>
       </c>
       <c r="F16">
-        <v>82656</v>
+        <v>87893</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2513,16 +2510,16 @@
         <v>32</v>
       </c>
       <c r="C17">
-        <v>181270</v>
+        <v>187698</v>
       </c>
       <c r="D17">
-        <v>28180</v>
+        <v>87822</v>
       </c>
       <c r="E17">
-        <v>93289</v>
+        <v>29653</v>
       </c>
       <c r="F17">
-        <v>87822</v>
+        <v>98163</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2533,16 +2530,16 @@
         <v>33</v>
       </c>
       <c r="C18">
-        <v>192543</v>
+        <v>199370</v>
       </c>
       <c r="D18">
-        <v>34526</v>
+        <v>95571</v>
       </c>
       <c r="E18">
-        <v>107667</v>
+        <v>36330</v>
       </c>
       <c r="F18">
-        <v>95571</v>
+        <v>113293</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2553,16 +2550,16 @@
         <v>34</v>
       </c>
       <c r="C19">
-        <v>199000</v>
+        <v>206057</v>
       </c>
       <c r="D19">
-        <v>41622</v>
+        <v>103320</v>
       </c>
       <c r="E19">
-        <v>133917</v>
+        <v>43797</v>
       </c>
       <c r="F19">
-        <v>103320</v>
+        <v>140914</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2573,16 +2570,16 @@
         <v>162</v>
       </c>
       <c r="C20">
-        <v>208179</v>
+        <v>215562</v>
       </c>
       <c r="D20">
-        <v>46356</v>
+        <v>108486</v>
       </c>
       <c r="E20">
-        <v>145665</v>
+        <v>48778</v>
       </c>
       <c r="F20">
-        <v>108486</v>
+        <v>153276</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2593,16 +2590,16 @@
         <v>35</v>
       </c>
       <c r="C21">
-        <v>182398</v>
+        <v>188866</v>
       </c>
       <c r="D21">
-        <v>25817</v>
+        <v>87822</v>
       </c>
       <c r="E21">
-        <v>97978</v>
+        <v>27166</v>
       </c>
       <c r="F21">
-        <v>87822</v>
+        <v>103097</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2613,16 +2610,16 @@
         <v>36</v>
       </c>
       <c r="C22">
-        <v>189123</v>
+        <v>195830</v>
       </c>
       <c r="D22">
-        <v>30543</v>
+        <v>92988</v>
       </c>
       <c r="E22">
-        <v>108004</v>
+        <v>32139</v>
       </c>
       <c r="F22">
-        <v>92988</v>
+        <v>113647</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2633,16 +2630,16 @@
         <v>37</v>
       </c>
       <c r="C23">
-        <v>201771</v>
+        <v>208926</v>
       </c>
       <c r="D23">
-        <v>36827</v>
+        <v>100737</v>
       </c>
       <c r="E23">
-        <v>122544</v>
+        <v>38751</v>
       </c>
       <c r="F23">
-        <v>100737</v>
+        <v>128947</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2653,16 +2650,16 @@
         <v>38</v>
       </c>
       <c r="C24">
-        <v>206798</v>
+        <v>214131</v>
       </c>
       <c r="D24">
-        <v>43986</v>
+        <v>108486</v>
       </c>
       <c r="E24">
-        <v>148314</v>
+        <v>46284</v>
       </c>
       <c r="F24">
-        <v>108486</v>
+        <v>156064</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2673,16 +2670,16 @@
         <v>39</v>
       </c>
       <c r="C25">
-        <v>216231</v>
+        <v>223898</v>
       </c>
       <c r="D25">
-        <v>48719</v>
+        <v>113652</v>
       </c>
       <c r="E25">
-        <v>160050</v>
+        <v>51265</v>
       </c>
       <c r="F25">
-        <v>113652</v>
+        <v>168412</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2693,16 +2690,16 @@
         <v>42</v>
       </c>
       <c r="C26">
-        <v>212113</v>
+        <v>219635</v>
       </c>
       <c r="D26">
-        <v>32107</v>
+        <v>103320</v>
       </c>
       <c r="E26">
-        <v>115394</v>
+        <v>33785</v>
       </c>
       <c r="F26">
-        <v>103320</v>
+        <v>121423</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2713,16 +2710,16 @@
         <v>43</v>
       </c>
       <c r="C27">
-        <v>219248</v>
+        <v>227023</v>
       </c>
       <c r="D27">
-        <v>39142</v>
+        <v>108486</v>
       </c>
       <c r="E27">
-        <v>139111</v>
+        <v>41187</v>
       </c>
       <c r="F27">
-        <v>108486</v>
+        <v>146379</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2733,16 +2730,16 @@
         <v>44</v>
       </c>
       <c r="C28">
-        <v>231875</v>
+        <v>240097</v>
       </c>
       <c r="D28">
-        <v>48719</v>
+        <v>116235</v>
       </c>
       <c r="E28">
-        <v>174480</v>
+        <v>51265</v>
       </c>
       <c r="F28">
-        <v>116235</v>
+        <v>183596</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2753,16 +2750,16 @@
         <v>45</v>
       </c>
       <c r="C29">
-        <v>237381</v>
+        <v>245798</v>
       </c>
       <c r="D29">
-        <v>59364</v>
+        <v>123984</v>
       </c>
       <c r="E29">
-        <v>210043</v>
+        <v>62466</v>
       </c>
       <c r="F29">
-        <v>123984</v>
+        <v>221017</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2773,16 +2770,16 @@
         <v>46</v>
       </c>
       <c r="C30">
-        <v>245960</v>
+        <v>254682</v>
       </c>
       <c r="D30">
-        <v>66468</v>
+        <v>129150</v>
       </c>
       <c r="E30">
-        <v>233760</v>
+        <v>69941</v>
       </c>
       <c r="F30">
-        <v>129150</v>
+        <v>245974</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2793,16 +2790,16 @@
         <v>18</v>
       </c>
       <c r="C31">
-        <v>260032</v>
+        <v>269253</v>
       </c>
       <c r="D31">
-        <v>28394</v>
+        <v>98154</v>
       </c>
       <c r="E31">
-        <v>100904</v>
+        <v>29877</v>
       </c>
       <c r="F31">
-        <v>98154</v>
+        <v>106176</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2813,16 +2810,16 @@
         <v>28</v>
       </c>
       <c r="C32">
-        <v>307140</v>
+        <v>318032</v>
       </c>
       <c r="D32">
-        <v>47321</v>
+        <v>129150</v>
       </c>
       <c r="E32">
-        <v>168171</v>
+        <v>49793</v>
       </c>
       <c r="F32">
-        <v>129150</v>
+        <v>176958</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2833,16 +2830,16 @@
         <v>162</v>
       </c>
       <c r="C33">
-        <v>324913</v>
+        <v>336435</v>
       </c>
       <c r="D33">
-        <v>52047</v>
+        <v>136899</v>
       </c>
       <c r="E33">
-        <v>184990</v>
+        <v>54767</v>
       </c>
       <c r="F33">
-        <v>136899</v>
+        <v>194655</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2853,16 +2850,16 @@
         <v>46</v>
       </c>
       <c r="C34">
-        <v>365825</v>
+        <v>378797</v>
       </c>
       <c r="D34">
-        <v>70981</v>
+        <v>167895</v>
       </c>
       <c r="E34">
-        <v>252257</v>
+        <v>74690</v>
       </c>
       <c r="F34">
-        <v>167895</v>
+        <v>265437</v>
       </c>
     </row>
   </sheetData>
@@ -3350,7 +3347,7 @@
         <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3745,170 +3742,170 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>193</v>
       </c>
       <c r="G26" s="1">
-        <v>1</v>
+        <v>320150</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>194</v>
       </c>
       <c r="G27" s="1">
-        <v>1</v>
+        <v>320150</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>195</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>320150</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="G30" s="1">
-        <v>1</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>194</v>
       </c>
       <c r="G31" s="1">
-        <v>1</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>195</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>295000</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>193</v>
       </c>
       <c r="G34" s="1">
-        <v>1</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>194</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>195</v>
       </c>
       <c r="G36" s="1">
-        <v>1</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>193</v>
       </c>
       <c r="G38" s="1">
-        <v>1</v>
+        <v>189680</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>194</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>189680</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>195</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>189680</v>
       </c>
     </row>
   </sheetData>
@@ -3936,7 +3933,7 @@
         <v>204</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>205</v>
@@ -4045,7 +4042,7 @@
         <v>221</v>
       </c>
       <c r="E9">
-        <v>18080</v>
+        <v>18622</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4056,7 +4053,7 @@
         <v>222</v>
       </c>
       <c r="E10">
-        <v>7400</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -4067,7 +4064,7 @@
         <v>223</v>
       </c>
       <c r="E11">
-        <v>4200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -4095,7 +4092,7 @@
         <v>221</v>
       </c>
       <c r="E13">
-        <v>20505</v>
+        <v>21120</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -4114,7 +4111,7 @@
         <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E15">
         <v>18500</v>
@@ -4136,7 +4133,7 @@
         <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C17" t="s">
         <v>227</v>
@@ -4150,7 +4147,7 @@
         <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C18" t="s">
         <v>190</v>
@@ -4164,13 +4161,13 @@
         <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
         <v>227</v>
       </c>
       <c r="D20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E20">
         <v>30208</v>
@@ -4181,13 +4178,13 @@
         <v>218</v>
       </c>
       <c r="B21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C21" t="s">
         <v>227</v>
       </c>
       <c r="D21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E21">
         <v>23180</v>
@@ -4198,13 +4195,13 @@
         <v>218</v>
       </c>
       <c r="B22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C22" t="s">
         <v>227</v>
       </c>
       <c r="D22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E22">
         <v>37410</v>
@@ -4215,13 +4212,13 @@
         <v>218</v>
       </c>
       <c r="B23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" t="s">
         <v>227</v>
       </c>
       <c r="D23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E23">
         <v>28263</v>
@@ -4232,13 +4229,13 @@
         <v>218</v>
       </c>
       <c r="B24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C24" t="s">
         <v>227</v>
       </c>
       <c r="D24" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E24">
         <v>52671</v>
@@ -4249,13 +4246,13 @@
         <v>218</v>
       </c>
       <c r="B25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C25" t="s">
         <v>227</v>
       </c>
       <c r="D25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E25">
         <v>39099</v>
@@ -4266,13 +4263,13 @@
         <v>218</v>
       </c>
       <c r="B27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C27" t="s">
         <v>190</v>
       </c>
       <c r="D27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E27">
         <v>188750</v>
@@ -4283,13 +4280,13 @@
         <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C28" t="s">
         <v>190</v>
       </c>
       <c r="D28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E28">
         <v>139851</v>
@@ -4300,13 +4297,13 @@
         <v>218</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C29" t="s">
         <v>190</v>
       </c>
       <c r="D29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E29">
         <v>204007</v>
@@ -4317,13 +4314,13 @@
         <v>218</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" t="s">
         <v>190</v>
       </c>
       <c r="D30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E30">
         <v>155108</v>
@@ -4381,7 +4378,7 @@
         <v>233</v>
       </c>
       <c r="E35">
-        <v>4000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -4392,7 +4389,7 @@
         <v>234</v>
       </c>
       <c r="E36">
-        <v>4000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -4403,7 +4400,7 @@
         <v>235</v>
       </c>
       <c r="E37">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -4488,7 +4485,7 @@
         <v>239</v>
       </c>
       <c r="B45" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E45">
         <v>225000</v>
@@ -4687,7 +4684,7 @@
         <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4698,7 +4695,7 @@
         <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4720,7 +4717,7 @@
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4731,7 +4728,7 @@
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4739,6 +4736,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4783,8 +4781,8 @@
       <c r="A5" t="s">
         <v>255</v>
       </c>
-      <c r="B5" t="s">
-        <v>256</v>
+      <c r="B5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4834,25 +4832,25 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>79094</v>
+        <v>81498</v>
       </c>
       <c r="C2" s="1">
         <v>7179</v>
       </c>
       <c r="D2" s="1">
-        <v>9900</v>
+        <v>10201</v>
       </c>
       <c r="E2" s="1">
-        <v>2709</v>
+        <v>2844</v>
       </c>
       <c r="F2" s="1">
-        <v>3275</v>
+        <v>3440</v>
       </c>
       <c r="G2" s="1">
-        <v>4312</v>
+        <v>4529</v>
       </c>
       <c r="H2" s="1">
-        <v>13501</v>
+        <v>14180</v>
       </c>
       <c r="I2" s="1">
         <v>36118</v>
@@ -4863,25 +4861,25 @@
         <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>86656</v>
+        <v>89291</v>
       </c>
       <c r="C3" s="1">
         <v>7179</v>
       </c>
       <c r="D3" s="1">
-        <v>11600</v>
+        <v>11953</v>
       </c>
       <c r="E3" s="1">
-        <v>3784</v>
+        <v>3972</v>
       </c>
       <c r="F3" s="1">
-        <v>4586</v>
+        <v>4816</v>
       </c>
       <c r="G3" s="1">
-        <v>6042</v>
+        <v>6346</v>
       </c>
       <c r="H3" s="1">
-        <v>18909</v>
+        <v>19860</v>
       </c>
       <c r="I3" s="1">
         <v>41278</v>
@@ -4893,25 +4891,25 @@
         <v>7</v>
       </c>
       <c r="B4" s="1">
-        <v>95394</v>
+        <v>98294</v>
       </c>
       <c r="C4" s="1">
         <v>7179</v>
       </c>
       <c r="D4" s="1">
-        <v>13300</v>
+        <v>13704</v>
       </c>
       <c r="E4" s="1">
-        <v>4865</v>
+        <v>5106</v>
       </c>
       <c r="F4" s="1">
-        <v>5902</v>
+        <v>6199</v>
       </c>
       <c r="G4" s="1">
-        <v>7766</v>
+        <v>8156</v>
       </c>
       <c r="H4" s="1">
-        <v>24309</v>
+        <v>25532</v>
       </c>
       <c r="I4" s="1">
         <v>46437</v>
@@ -4922,25 +4920,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="1">
-        <v>104138</v>
+        <v>107303</v>
       </c>
       <c r="C5" s="1">
         <v>7179</v>
       </c>
       <c r="D5" s="1">
-        <v>15000</v>
+        <v>15456</v>
       </c>
       <c r="E5" s="1">
-        <v>5959</v>
+        <v>6254</v>
       </c>
       <c r="F5" s="1">
-        <v>7212</v>
+        <v>7575</v>
       </c>
       <c r="G5" s="1">
-        <v>9495</v>
+        <v>9973</v>
       </c>
       <c r="H5" s="1">
-        <v>29710</v>
+        <v>31204</v>
       </c>
       <c r="I5" s="1">
         <v>51597</v>
@@ -4951,25 +4949,25 @@
         <v>9</v>
       </c>
       <c r="B6" s="1">
-        <v>119019</v>
+        <v>122637</v>
       </c>
       <c r="C6" s="1">
         <v>7179</v>
       </c>
       <c r="D6" s="1">
-        <v>17550</v>
+        <v>18084</v>
       </c>
       <c r="E6" s="1">
-        <v>7568</v>
+        <v>7943</v>
       </c>
       <c r="F6" s="1">
-        <v>9171</v>
+        <v>9633</v>
       </c>
       <c r="G6" s="1">
-        <v>12078</v>
+        <v>12685</v>
       </c>
       <c r="H6" s="1">
-        <v>37810</v>
+        <v>39713</v>
       </c>
       <c r="I6" s="1">
         <v>59337</v>
@@ -4980,25 +4978,25 @@
         <v>10</v>
       </c>
       <c r="B7" s="1">
-        <v>134413</v>
+        <v>138499</v>
       </c>
       <c r="C7" s="1">
         <v>7179</v>
       </c>
       <c r="D7" s="1">
-        <v>20100</v>
+        <v>20711</v>
       </c>
       <c r="E7" s="1">
-        <v>9197</v>
+        <v>9652</v>
       </c>
       <c r="F7" s="1">
-        <v>11136</v>
+        <v>11697</v>
       </c>
       <c r="G7" s="1">
-        <v>14666</v>
+        <v>15404</v>
       </c>
       <c r="H7" s="1">
-        <v>45918</v>
+        <v>48229</v>
       </c>
       <c r="I7" s="1">
         <v>67076</v>
@@ -5009,25 +5007,25 @@
         <v>11</v>
       </c>
       <c r="B8" s="1">
-        <v>149738</v>
+        <v>154290</v>
       </c>
       <c r="C8" s="1">
         <v>7179</v>
       </c>
       <c r="D8" s="1">
-        <v>21800</v>
+        <v>22463</v>
       </c>
       <c r="E8" s="1">
-        <v>10278</v>
+        <v>10787</v>
       </c>
       <c r="F8" s="1">
-        <v>12453</v>
+        <v>13079</v>
       </c>
       <c r="G8" s="1">
-        <v>16390</v>
+        <v>17214</v>
       </c>
       <c r="H8" s="1">
-        <v>51326</v>
+        <v>53908</v>
       </c>
       <c r="I8" s="1">
         <v>72236</v>
@@ -5038,25 +5036,25 @@
         <v>12</v>
       </c>
       <c r="B9" s="1">
-        <v>89188</v>
+        <v>91899</v>
       </c>
       <c r="C9" s="1">
         <v>10768</v>
       </c>
       <c r="D9" s="1">
-        <v>13050</v>
+        <v>13447</v>
       </c>
       <c r="E9" s="1">
-        <v>4509</v>
+        <v>4733</v>
       </c>
       <c r="F9" s="1">
-        <v>5457</v>
+        <v>5731</v>
       </c>
       <c r="G9" s="1">
-        <v>7193</v>
+        <v>7555</v>
       </c>
       <c r="H9" s="1">
-        <v>22509</v>
+        <v>23642</v>
       </c>
       <c r="I9" s="1">
         <v>46437</v>
@@ -5067,25 +5065,25 @@
         <v>13</v>
       </c>
       <c r="B10" s="1">
-        <v>96781</v>
+        <v>99723</v>
       </c>
       <c r="C10" s="1">
         <v>10768</v>
       </c>
       <c r="D10" s="1">
-        <v>15000</v>
+        <v>15456</v>
       </c>
       <c r="E10" s="1">
-        <v>6309</v>
+        <v>6622</v>
       </c>
       <c r="F10" s="1">
-        <v>7645</v>
+        <v>8029</v>
       </c>
       <c r="G10" s="1">
-        <v>10068</v>
+        <v>10574</v>
       </c>
       <c r="H10" s="1">
-        <v>31510</v>
+        <v>33095</v>
       </c>
       <c r="I10" s="1">
         <v>51597</v>
@@ -5096,25 +5094,25 @@
         <v>14</v>
       </c>
       <c r="B11" s="1">
-        <v>105619</v>
+        <v>108830</v>
       </c>
       <c r="C11" s="1">
         <v>10768</v>
       </c>
       <c r="D11" s="1">
-        <v>16950</v>
+        <v>17465</v>
       </c>
       <c r="E11" s="1">
-        <v>8115</v>
+        <v>8517</v>
       </c>
       <c r="F11" s="1">
-        <v>9826</v>
+        <v>10321</v>
       </c>
       <c r="G11" s="1">
-        <v>12943</v>
+        <v>13594</v>
       </c>
       <c r="H11" s="1">
-        <v>40518</v>
+        <v>42556</v>
       </c>
       <c r="I11" s="1">
         <v>56757</v>
@@ -5125,25 +5123,25 @@
         <v>15</v>
       </c>
       <c r="B12" s="1">
-        <v>114369</v>
+        <v>117846</v>
       </c>
       <c r="C12" s="1">
         <v>10768</v>
       </c>
       <c r="D12" s="1">
-        <v>18900</v>
+        <v>19475</v>
       </c>
       <c r="E12" s="1">
-        <v>9915</v>
+        <v>10406</v>
       </c>
       <c r="F12" s="1">
-        <v>12014</v>
+        <v>12619</v>
       </c>
       <c r="G12" s="1">
-        <v>15817</v>
+        <v>16613</v>
       </c>
       <c r="H12" s="1">
-        <v>49518</v>
+        <v>52010</v>
       </c>
       <c r="I12" s="1">
         <v>61916</v>
@@ -5154,25 +5152,25 @@
         <v>16</v>
       </c>
       <c r="B13" s="1">
-        <v>129250</v>
+        <v>133179</v>
       </c>
       <c r="C13" s="1">
         <v>10768</v>
       </c>
       <c r="D13" s="1">
-        <v>21825</v>
+        <v>22488</v>
       </c>
       <c r="E13" s="1">
-        <v>12625</v>
+        <v>13250</v>
       </c>
       <c r="F13" s="1">
-        <v>15289</v>
+        <v>16059</v>
       </c>
       <c r="G13" s="1">
-        <v>20129</v>
+        <v>21142</v>
       </c>
       <c r="H13" s="1">
-        <v>63027</v>
+        <v>66198</v>
       </c>
       <c r="I13" s="1">
         <v>69656</v>
@@ -5183,25 +5181,25 @@
         <v>17</v>
       </c>
       <c r="B14" s="1">
-        <v>144138</v>
+        <v>148519</v>
       </c>
       <c r="C14" s="1">
         <v>10768</v>
       </c>
       <c r="D14" s="1">
-        <v>24750</v>
+        <v>25502</v>
       </c>
       <c r="E14" s="1">
-        <v>15328</v>
+        <v>16087</v>
       </c>
       <c r="F14" s="1">
-        <v>18565</v>
+        <v>19499</v>
       </c>
       <c r="G14" s="1">
-        <v>24448</v>
+        <v>25678</v>
       </c>
       <c r="H14" s="1">
-        <v>76528</v>
+        <v>80378</v>
       </c>
       <c r="I14" s="1">
         <v>77396</v>
@@ -5212,25 +5210,25 @@
         <v>18</v>
       </c>
       <c r="B15" s="1">
-        <v>159969</v>
+        <v>164832</v>
       </c>
       <c r="C15" s="1">
         <v>10768</v>
       </c>
       <c r="D15" s="1">
-        <v>26700</v>
+        <v>27512</v>
       </c>
       <c r="E15" s="1">
-        <v>17127</v>
+        <v>17976</v>
       </c>
       <c r="F15" s="1">
-        <v>20746</v>
+        <v>21790</v>
       </c>
       <c r="G15" s="1">
-        <v>27323</v>
+        <v>28697</v>
       </c>
       <c r="H15" s="1">
-        <v>85536</v>
+        <v>89840</v>
       </c>
       <c r="I15" s="1">
         <v>82555</v>
@@ -5241,25 +5239,25 @@
         <v>19</v>
       </c>
       <c r="B16" s="1">
-        <v>115844</v>
+        <v>119365</v>
       </c>
       <c r="C16" s="1">
         <v>14358</v>
       </c>
       <c r="D16" s="1">
-        <v>20600</v>
+        <v>21226</v>
       </c>
       <c r="E16" s="1">
-        <v>11359</v>
+        <v>11922</v>
       </c>
       <c r="F16" s="1">
-        <v>13757</v>
+        <v>14449</v>
       </c>
       <c r="G16" s="1">
-        <v>18120</v>
+        <v>19031</v>
       </c>
       <c r="H16" s="1">
-        <v>56726</v>
+        <v>59581</v>
       </c>
       <c r="I16" s="1">
         <v>67076</v>
@@ -5270,25 +5268,25 @@
         <v>20</v>
       </c>
       <c r="B17" s="1">
-        <v>124588</v>
+        <v>128375</v>
       </c>
       <c r="C17" s="1">
         <v>14358</v>
       </c>
       <c r="D17" s="1">
-        <v>22800</v>
+        <v>23493</v>
       </c>
       <c r="E17" s="1">
-        <v>13884</v>
+        <v>14572</v>
       </c>
       <c r="F17" s="1">
-        <v>16816</v>
+        <v>17662</v>
       </c>
       <c r="G17" s="1">
-        <v>22146</v>
+        <v>23260</v>
       </c>
       <c r="H17" s="1">
-        <v>69327</v>
+        <v>72815</v>
       </c>
       <c r="I17" s="1">
         <v>72236</v>
@@ -5299,25 +5297,25 @@
         <v>21</v>
       </c>
       <c r="B18" s="1">
-        <v>139475</v>
+        <v>143715</v>
       </c>
       <c r="C18" s="1">
         <v>14358</v>
       </c>
       <c r="D18" s="1">
-        <v>26100</v>
+        <v>26893</v>
       </c>
       <c r="E18" s="1">
-        <v>17668</v>
+        <v>18543</v>
       </c>
       <c r="F18" s="1">
-        <v>21401</v>
+        <v>22478</v>
       </c>
       <c r="G18" s="1">
-        <v>28188</v>
+        <v>29606</v>
       </c>
       <c r="H18" s="1">
-        <v>88236</v>
+        <v>92676</v>
       </c>
       <c r="I18" s="1">
         <v>79975</v>
@@ -5328,25 +5326,25 @@
         <v>22</v>
       </c>
       <c r="B19" s="1">
-        <v>154356</v>
+        <v>159049</v>
       </c>
       <c r="C19" s="1">
         <v>14358</v>
       </c>
       <c r="D19" s="1">
-        <v>29400</v>
+        <v>30294</v>
       </c>
       <c r="E19" s="1">
-        <v>21459</v>
+        <v>22521</v>
       </c>
       <c r="F19" s="1">
-        <v>25987</v>
+        <v>27294</v>
       </c>
       <c r="G19" s="1">
-        <v>34230</v>
+        <v>35952</v>
       </c>
       <c r="H19" s="1">
-        <v>107145</v>
+        <v>112536</v>
       </c>
       <c r="I19" s="1">
         <v>87715</v>
@@ -5357,25 +5355,25 @@
         <v>23</v>
       </c>
       <c r="B20" s="1">
-        <v>170325</v>
+        <v>175503</v>
       </c>
       <c r="C20" s="1">
         <v>14358</v>
       </c>
       <c r="D20" s="1">
-        <v>31600</v>
+        <v>32561</v>
       </c>
       <c r="E20" s="1">
-        <v>23977</v>
+        <v>25165</v>
       </c>
       <c r="F20" s="1">
-        <v>29046</v>
+        <v>30508</v>
       </c>
       <c r="G20" s="1">
-        <v>38249</v>
+        <v>40174</v>
       </c>
       <c r="H20" s="1">
-        <v>119746</v>
+        <v>125771</v>
       </c>
       <c r="I20" s="1">
         <v>92875</v>
@@ -5386,25 +5384,25 @@
         <v>24</v>
       </c>
       <c r="B21" s="1">
-        <v>124919</v>
+        <v>128716</v>
       </c>
       <c r="C21" s="1">
         <v>17946</v>
       </c>
       <c r="D21" s="1">
-        <v>24250</v>
+        <v>24987</v>
       </c>
       <c r="E21" s="1">
-        <v>14603</v>
+        <v>15326</v>
       </c>
       <c r="F21" s="1">
-        <v>17694</v>
+        <v>18584</v>
       </c>
       <c r="G21" s="1">
-        <v>23297</v>
+        <v>24469</v>
       </c>
       <c r="H21" s="1">
-        <v>72935</v>
+        <v>76605</v>
       </c>
       <c r="I21" s="1">
         <v>77396</v>
@@ -5415,25 +5413,25 @@
         <v>25</v>
       </c>
       <c r="B22" s="1">
-        <v>132888</v>
+        <v>136927</v>
       </c>
       <c r="C22" s="1">
         <v>17946</v>
       </c>
       <c r="D22" s="1">
-        <v>26700</v>
+        <v>27512</v>
       </c>
       <c r="E22" s="1">
-        <v>17853</v>
+        <v>18737</v>
       </c>
       <c r="F22" s="1">
-        <v>21624</v>
+        <v>22712</v>
       </c>
       <c r="G22" s="1">
-        <v>28474</v>
+        <v>29906</v>
       </c>
       <c r="H22" s="1">
-        <v>89136</v>
+        <v>93621</v>
       </c>
       <c r="I22" s="1">
         <v>82555</v>
@@ -5444,25 +5442,25 @@
         <v>26</v>
       </c>
       <c r="B23" s="1">
-        <v>147769</v>
+        <v>152261</v>
       </c>
       <c r="C23" s="1">
         <v>17946</v>
       </c>
       <c r="D23" s="1">
-        <v>30375</v>
+        <v>31298</v>
       </c>
       <c r="E23" s="1">
-        <v>22718</v>
+        <v>23843</v>
       </c>
       <c r="F23" s="1">
-        <v>27520</v>
+        <v>28904</v>
       </c>
       <c r="G23" s="1">
-        <v>36239</v>
+        <v>38063</v>
       </c>
       <c r="H23" s="1">
-        <v>113445</v>
+        <v>119153</v>
       </c>
       <c r="I23" s="1">
         <v>90295</v>
@@ -5473,25 +5471,25 @@
         <v>27</v>
       </c>
       <c r="B24" s="1">
-        <v>162644</v>
+        <v>167588</v>
       </c>
       <c r="C24" s="1">
         <v>17946</v>
       </c>
       <c r="D24" s="1">
-        <v>34050</v>
+        <v>35085</v>
       </c>
       <c r="E24" s="1">
-        <v>27583</v>
+        <v>28949</v>
       </c>
       <c r="F24" s="1">
-        <v>33415</v>
+        <v>35097</v>
       </c>
       <c r="G24" s="1">
-        <v>41416</v>
+        <v>43500</v>
       </c>
       <c r="H24" s="1">
-        <v>137755</v>
+        <v>144686</v>
       </c>
       <c r="I24" s="1">
         <v>98034</v>
@@ -5502,25 +5500,25 @@
         <v>28</v>
       </c>
       <c r="B25" s="1">
-        <v>177156</v>
+        <v>182542</v>
       </c>
       <c r="C25" s="1">
         <v>17946</v>
       </c>
       <c r="D25" s="1">
-        <v>36500</v>
+        <v>37610</v>
       </c>
       <c r="E25" s="1">
-        <v>30833</v>
+        <v>32360</v>
       </c>
       <c r="F25" s="1">
-        <v>37346</v>
+        <v>39225</v>
       </c>
       <c r="G25" s="1">
-        <v>47535</v>
+        <v>49926</v>
       </c>
       <c r="H25" s="1">
-        <v>153963</v>
+        <v>161710</v>
       </c>
       <c r="I25" s="1">
         <v>103194</v>
@@ -5531,25 +5529,25 @@
         <v>29</v>
       </c>
       <c r="B26" s="1">
-        <v>188250</v>
+        <v>193973</v>
       </c>
       <c r="C26" s="1">
         <v>17946</v>
       </c>
       <c r="D26" s="1">
-        <v>38950</v>
+        <v>40134</v>
       </c>
       <c r="E26" s="1">
-        <v>34077</v>
+        <v>35765</v>
       </c>
       <c r="F26" s="1">
-        <v>41276</v>
+        <v>43353</v>
       </c>
       <c r="G26" s="1">
-        <v>54359</v>
+        <v>57094</v>
       </c>
       <c r="H26" s="1">
-        <v>170172</v>
+        <v>178734</v>
       </c>
       <c r="I26" s="1">
         <v>108354</v>
@@ -5560,25 +5558,25 @@
         <v>30</v>
       </c>
       <c r="B27" s="1">
-        <v>199994</v>
+        <v>206074</v>
       </c>
       <c r="C27" s="1">
         <v>17946</v>
       </c>
       <c r="D27" s="1">
-        <v>41400</v>
+        <v>42659</v>
       </c>
       <c r="E27" s="1">
-        <v>37320</v>
+        <v>39169</v>
       </c>
       <c r="F27" s="1">
-        <v>45207</v>
+        <v>47481</v>
       </c>
       <c r="G27" s="1">
-        <v>59536</v>
+        <v>62531</v>
       </c>
       <c r="H27" s="1">
-        <v>186373</v>
+        <v>195750</v>
       </c>
       <c r="I27" s="1">
         <v>113513</v>
@@ -5589,25 +5587,25 @@
         <v>31</v>
       </c>
       <c r="B28" s="1">
-        <v>127825</v>
+        <v>131711</v>
       </c>
       <c r="C28" s="1">
         <v>19741</v>
       </c>
       <c r="D28" s="1">
-        <v>26075</v>
+        <v>26868</v>
       </c>
       <c r="E28" s="1">
-        <v>16231</v>
+        <v>17035</v>
       </c>
       <c r="F28" s="1">
-        <v>19659</v>
+        <v>20648</v>
       </c>
       <c r="G28" s="1">
-        <v>25885</v>
+        <v>27188</v>
       </c>
       <c r="H28" s="1">
-        <v>81036</v>
+        <v>85113</v>
       </c>
       <c r="I28" s="1">
         <v>82555</v>
@@ -5618,25 +5616,25 @@
         <v>32</v>
       </c>
       <c r="B29" s="1">
-        <v>137575</v>
+        <v>141757</v>
       </c>
       <c r="C29" s="1">
         <v>19741</v>
       </c>
       <c r="D29" s="1">
-        <v>28650</v>
+        <v>29521</v>
       </c>
       <c r="E29" s="1">
-        <v>19830</v>
+        <v>20813</v>
       </c>
       <c r="F29" s="1">
-        <v>24022</v>
+        <v>25230</v>
       </c>
       <c r="G29" s="1">
-        <v>31635</v>
+        <v>33226</v>
       </c>
       <c r="H29" s="1">
-        <v>99037</v>
+        <v>104020</v>
       </c>
       <c r="I29" s="1">
         <v>87715</v>
@@ -5647,25 +5645,25 @@
         <v>33</v>
       </c>
       <c r="B30" s="1">
-        <v>155000</v>
+        <v>159712</v>
       </c>
       <c r="C30" s="1">
         <v>19741</v>
       </c>
       <c r="D30" s="1">
-        <v>32513</v>
+        <v>33501</v>
       </c>
       <c r="E30" s="1">
-        <v>25243</v>
+        <v>26493</v>
       </c>
       <c r="F30" s="1">
-        <v>30579</v>
+        <v>32117</v>
       </c>
       <c r="G30" s="1">
-        <v>40265</v>
+        <v>42291</v>
       </c>
       <c r="H30" s="1">
-        <v>126054</v>
+        <v>132396</v>
       </c>
       <c r="I30" s="1">
         <v>95454</v>
@@ -5676,25 +5674,25 @@
         <v>34</v>
       </c>
       <c r="B31" s="1">
-        <v>166338</v>
+        <v>171394</v>
       </c>
       <c r="C31" s="1">
         <v>19741</v>
       </c>
       <c r="D31" s="1">
-        <v>36375</v>
+        <v>37481</v>
       </c>
       <c r="E31" s="1">
-        <v>30655</v>
+        <v>32174</v>
       </c>
       <c r="F31" s="1">
-        <v>37130</v>
+        <v>38998</v>
       </c>
       <c r="G31" s="1">
-        <v>48889</v>
+        <v>51349</v>
       </c>
       <c r="H31" s="1">
-        <v>153056</v>
+        <v>160757</v>
       </c>
       <c r="I31" s="1">
         <v>103194</v>
@@ -5705,25 +5703,25 @@
         <v>163</v>
       </c>
       <c r="B32" s="1">
-        <v>197481</v>
+        <v>203485</v>
       </c>
       <c r="C32" s="1">
         <v>19741</v>
       </c>
       <c r="D32" s="1">
-        <v>41525</v>
+        <v>42787</v>
       </c>
       <c r="E32" s="1">
-        <v>37861</v>
+        <v>39736</v>
       </c>
       <c r="F32" s="1">
-        <v>45862</v>
+        <v>48169</v>
       </c>
       <c r="G32" s="1">
-        <v>60395</v>
+        <v>63433</v>
       </c>
       <c r="H32" s="1">
-        <v>189073</v>
+        <v>198586</v>
       </c>
       <c r="I32" s="1">
         <v>113513</v>
@@ -5734,25 +5732,25 @@
         <v>164</v>
       </c>
       <c r="B33" s="1">
-        <v>212169</v>
+        <v>218619</v>
       </c>
       <c r="C33" s="1">
         <v>19741</v>
       </c>
       <c r="D33" s="1">
-        <v>44100</v>
+        <v>45441</v>
       </c>
       <c r="E33" s="1">
-        <v>41467</v>
+        <v>43521</v>
       </c>
       <c r="F33" s="1">
-        <v>50231</v>
+        <v>52759</v>
       </c>
       <c r="G33" s="1">
-        <v>66150</v>
+        <v>69479</v>
       </c>
       <c r="H33" s="1">
-        <v>207082</v>
+        <v>217501</v>
       </c>
       <c r="I33" s="1">
         <v>118673</v>
@@ -5763,25 +5761,25 @@
         <v>35</v>
       </c>
       <c r="B34" s="1">
-        <v>135138</v>
+        <v>139246</v>
       </c>
       <c r="C34" s="1">
         <v>21535</v>
       </c>
       <c r="D34" s="1">
-        <v>27900</v>
+        <v>28748</v>
       </c>
       <c r="E34" s="1">
-        <v>17853</v>
+        <v>18737</v>
       </c>
       <c r="F34" s="1">
-        <v>21624</v>
+        <v>22712</v>
       </c>
       <c r="G34" s="1">
-        <v>28474</v>
+        <v>29906</v>
       </c>
       <c r="H34" s="1">
-        <v>89136</v>
+        <v>93621</v>
       </c>
       <c r="I34" s="1">
         <v>87715</v>
@@ -5792,25 +5790,25 @@
         <v>36</v>
       </c>
       <c r="B35" s="1">
-        <v>143875</v>
+        <v>148249</v>
       </c>
       <c r="C35" s="1">
         <v>21535</v>
       </c>
       <c r="D35" s="1">
-        <v>30600</v>
+        <v>31530</v>
       </c>
       <c r="E35" s="1">
-        <v>21815</v>
+        <v>22895</v>
       </c>
       <c r="F35" s="1">
-        <v>26426</v>
+        <v>27755</v>
       </c>
       <c r="G35" s="1">
-        <v>31635</v>
+        <v>33226</v>
       </c>
       <c r="H35" s="1">
-        <v>108945</v>
+        <v>114427</v>
       </c>
       <c r="I35" s="1">
         <v>92875</v>
@@ -5821,25 +5819,25 @@
         <v>37</v>
       </c>
       <c r="B36" s="1">
-        <v>159944</v>
+        <v>164806</v>
       </c>
       <c r="C36" s="1">
         <v>21535</v>
       </c>
       <c r="D36" s="1">
-        <v>34650</v>
+        <v>35703</v>
       </c>
       <c r="E36" s="1">
-        <v>27768</v>
+        <v>29143</v>
       </c>
       <c r="F36" s="1">
-        <v>33632</v>
+        <v>35324</v>
       </c>
       <c r="G36" s="1">
-        <v>44291</v>
+        <v>46520</v>
       </c>
       <c r="H36" s="1">
-        <v>138655</v>
+        <v>145631</v>
       </c>
       <c r="I36" s="1">
         <v>100614</v>
@@ -5850,25 +5848,25 @@
         <v>38</v>
       </c>
       <c r="B37" s="1">
-        <v>173644</v>
+        <v>178923</v>
       </c>
       <c r="C37" s="1">
         <v>21535</v>
       </c>
       <c r="D37" s="1">
-        <v>38700</v>
+        <v>39876</v>
       </c>
       <c r="E37" s="1">
-        <v>33714</v>
+        <v>35384</v>
       </c>
       <c r="F37" s="1">
-        <v>40844</v>
+        <v>42899</v>
       </c>
       <c r="G37" s="1">
-        <v>53780</v>
+        <v>56486</v>
       </c>
       <c r="H37" s="1">
-        <v>168364</v>
+        <v>176835</v>
       </c>
       <c r="I37" s="1">
         <v>108354</v>
@@ -5879,25 +5877,25 @@
         <v>39</v>
       </c>
       <c r="B38" s="1">
-        <v>189481</v>
+        <v>195241</v>
       </c>
       <c r="C38" s="1">
         <v>21535</v>
       </c>
       <c r="D38" s="1">
-        <v>41400</v>
+        <v>42659</v>
       </c>
       <c r="E38" s="1">
-        <v>37683</v>
+        <v>39549</v>
       </c>
       <c r="F38" s="1">
-        <v>45646</v>
+        <v>47942</v>
       </c>
       <c r="G38" s="1">
-        <v>60108</v>
+        <v>63133</v>
       </c>
       <c r="H38" s="1">
-        <v>188173</v>
+        <v>197641</v>
       </c>
       <c r="I38" s="1">
         <v>113513</v>
@@ -5908,25 +5906,25 @@
         <v>40</v>
       </c>
       <c r="B39" s="1">
-        <v>205731</v>
+        <v>211985</v>
       </c>
       <c r="C39" s="1">
         <v>21535</v>
       </c>
       <c r="D39" s="1">
-        <v>44100</v>
+        <v>45441</v>
       </c>
       <c r="E39" s="1">
-        <v>41652</v>
+        <v>43715</v>
       </c>
       <c r="F39" s="1">
-        <v>50454</v>
+        <v>52992</v>
       </c>
       <c r="G39" s="1">
-        <v>66437</v>
+        <v>69779</v>
       </c>
       <c r="H39" s="1">
-        <v>207982</v>
+        <v>218446</v>
       </c>
       <c r="I39" s="1">
         <v>118673</v>
@@ -5937,25 +5935,25 @@
         <v>41</v>
       </c>
       <c r="B40" s="1">
-        <v>218806</v>
+        <v>225458</v>
       </c>
       <c r="C40" s="1">
         <v>21535</v>
       </c>
       <c r="D40" s="1">
-        <v>46800</v>
+        <v>48223</v>
       </c>
       <c r="E40" s="1">
-        <v>45620</v>
+        <v>47880</v>
       </c>
       <c r="F40" s="1">
-        <v>55256</v>
+        <v>58036</v>
       </c>
       <c r="G40" s="1">
-        <v>72765</v>
+        <v>76426</v>
       </c>
       <c r="H40" s="1">
-        <v>227791</v>
+        <v>239252</v>
       </c>
       <c r="I40" s="1">
         <v>123833</v>
@@ -5966,25 +5964,25 @@
         <v>42</v>
       </c>
       <c r="B41" s="1">
-        <v>145750</v>
+        <v>150181</v>
       </c>
       <c r="C41" s="1">
         <v>26919</v>
       </c>
       <c r="D41" s="1">
-        <v>33375</v>
+        <v>34390</v>
       </c>
       <c r="E41" s="1">
-        <v>22718</v>
+        <v>23843</v>
       </c>
       <c r="F41" s="1">
-        <v>27520</v>
+        <v>28904</v>
       </c>
       <c r="G41" s="1">
-        <v>36239</v>
+        <v>38063</v>
       </c>
       <c r="H41" s="1">
-        <v>113445</v>
+        <v>119153</v>
       </c>
       <c r="I41" s="1">
         <v>103194</v>
@@ -5995,25 +5993,25 @@
         <v>43</v>
       </c>
       <c r="B42" s="1">
-        <v>154494</v>
+        <v>159190</v>
       </c>
       <c r="C42" s="1">
         <v>26919</v>
       </c>
       <c r="D42" s="1">
-        <v>36450</v>
+        <v>37558</v>
       </c>
       <c r="E42" s="1">
-        <v>27768</v>
+        <v>29143</v>
       </c>
       <c r="F42" s="1">
-        <v>33632</v>
+        <v>35324</v>
       </c>
       <c r="G42" s="1">
-        <v>44291</v>
+        <v>46520</v>
       </c>
       <c r="H42" s="1">
-        <v>138655</v>
+        <v>145631</v>
       </c>
       <c r="I42" s="1">
         <v>108354</v>
@@ -6024,25 +6022,25 @@
         <v>44</v>
       </c>
       <c r="B43" s="1">
-        <v>171738</v>
+        <v>176958</v>
       </c>
       <c r="C43" s="1">
         <v>26919</v>
       </c>
       <c r="D43" s="1">
-        <v>41063</v>
+        <v>42311</v>
       </c>
       <c r="E43" s="1">
-        <v>35336</v>
+        <v>37086</v>
       </c>
       <c r="F43" s="1">
-        <v>42809</v>
+        <v>44963</v>
       </c>
       <c r="G43" s="1">
-        <v>56369</v>
+        <v>59205</v>
       </c>
       <c r="H43" s="1">
-        <v>176472</v>
+        <v>185351</v>
       </c>
       <c r="I43" s="1">
         <v>116093</v>
@@ -6053,25 +6051,25 @@
         <v>45</v>
       </c>
       <c r="B44" s="1">
-        <v>184256</v>
+        <v>189858</v>
       </c>
       <c r="C44" s="1">
         <v>26919</v>
       </c>
       <c r="D44" s="1">
-        <v>45675</v>
+        <v>47064</v>
       </c>
       <c r="E44" s="1">
-        <v>42911</v>
+        <v>45036</v>
       </c>
       <c r="F44" s="1">
-        <v>51974</v>
+        <v>54589</v>
       </c>
       <c r="G44" s="1">
-        <v>68446</v>
+        <v>71890</v>
       </c>
       <c r="H44" s="1">
-        <v>214282</v>
+        <v>225064</v>
       </c>
       <c r="I44" s="1">
         <v>123833</v>
@@ -6082,25 +6080,25 @@
         <v>46</v>
       </c>
       <c r="B45" s="1">
-        <v>200094</v>
+        <v>206177</v>
       </c>
       <c r="C45" s="1">
         <v>26919</v>
       </c>
       <c r="D45" s="1">
-        <v>48750</v>
+        <v>50232</v>
       </c>
       <c r="E45" s="1">
-        <v>47961</v>
+        <v>50336</v>
       </c>
       <c r="F45" s="1">
-        <v>51732</v>
+        <v>54335</v>
       </c>
       <c r="G45" s="1">
-        <v>76504</v>
+        <v>80354</v>
       </c>
       <c r="H45" s="1">
-        <v>239506</v>
+        <v>251557</v>
       </c>
       <c r="I45" s="1">
         <v>128993</v>
@@ -6111,25 +6109,25 @@
         <v>47</v>
       </c>
       <c r="B46" s="1">
-        <v>217975</v>
+        <v>224601</v>
       </c>
       <c r="C46" s="1">
         <v>26919</v>
       </c>
       <c r="D46" s="1">
-        <v>51825</v>
+        <v>53400</v>
       </c>
       <c r="E46" s="1">
-        <v>53004</v>
+        <v>55629</v>
       </c>
       <c r="F46" s="1">
-        <v>64211</v>
+        <v>67441</v>
       </c>
       <c r="G46" s="1">
-        <v>84556</v>
+        <v>88811</v>
       </c>
       <c r="H46" s="1">
-        <v>264701</v>
+        <v>278019</v>
       </c>
       <c r="I46" s="1">
         <v>134152</v>
@@ -6140,25 +6138,25 @@
         <v>48</v>
       </c>
       <c r="B47" s="1">
-        <v>229094</v>
+        <v>236058</v>
       </c>
       <c r="C47" s="1">
         <v>26919</v>
       </c>
       <c r="D47" s="1">
-        <v>54900</v>
+        <v>56569</v>
       </c>
       <c r="E47" s="1">
-        <v>58060</v>
+        <v>60936</v>
       </c>
       <c r="F47" s="1">
-        <v>70323</v>
+        <v>73861</v>
       </c>
       <c r="G47" s="1">
-        <v>92608</v>
+        <v>97267</v>
       </c>
       <c r="H47" s="1">
-        <v>289918</v>
+        <v>304505</v>
       </c>
       <c r="I47" s="1">
         <v>139312</v>
@@ -6169,25 +6167,25 @@
         <v>49</v>
       </c>
       <c r="B48" s="1">
-        <v>193250</v>
+        <v>199125</v>
       </c>
       <c r="C48" s="1">
         <v>35893</v>
       </c>
       <c r="D48" s="1">
-        <v>42500</v>
+        <v>43792</v>
       </c>
       <c r="E48" s="1">
-        <v>30833</v>
+        <v>32360</v>
       </c>
       <c r="F48" s="1">
-        <v>37346</v>
+        <v>39225</v>
       </c>
       <c r="G48" s="1">
-        <v>49182</v>
+        <v>51656</v>
       </c>
       <c r="H48" s="1">
-        <v>153956</v>
+        <v>161702</v>
       </c>
       <c r="I48" s="1">
         <v>128993</v>
@@ -6198,25 +6196,25 @@
         <v>50</v>
       </c>
       <c r="B49" s="1">
-        <v>208394</v>
+        <v>214729</v>
       </c>
       <c r="C49" s="1">
         <v>35893</v>
       </c>
       <c r="D49" s="1">
-        <v>46200</v>
+        <v>47604</v>
       </c>
       <c r="E49" s="1">
-        <v>37683</v>
+        <v>39549</v>
       </c>
       <c r="F49" s="1">
-        <v>45646</v>
+        <v>47942</v>
       </c>
       <c r="G49" s="1">
-        <v>60108</v>
+        <v>63133</v>
       </c>
       <c r="H49" s="1">
-        <v>188173</v>
+        <v>197641</v>
       </c>
       <c r="I49" s="1">
         <v>134152</v>
@@ -6227,25 +6225,25 @@
         <v>51</v>
       </c>
       <c r="B50" s="1">
-        <v>225888</v>
+        <v>232754</v>
       </c>
       <c r="C50" s="1">
         <v>35893</v>
       </c>
       <c r="D50" s="1">
-        <v>51750</v>
+        <v>53323</v>
       </c>
       <c r="E50" s="1">
-        <v>50486</v>
+        <v>52986</v>
       </c>
       <c r="F50" s="1">
-        <v>58092</v>
+        <v>61015</v>
       </c>
       <c r="G50" s="1">
-        <v>76504</v>
+        <v>80354</v>
       </c>
       <c r="H50" s="1">
-        <v>239499</v>
+        <v>251549</v>
       </c>
       <c r="I50" s="1">
         <v>141892</v>
@@ -6256,25 +6254,25 @@
         <v>52</v>
       </c>
       <c r="B51" s="1">
-        <v>240975</v>
+        <v>248301</v>
       </c>
       <c r="C51" s="1">
         <v>35893</v>
       </c>
       <c r="D51" s="1">
-        <v>57300</v>
+        <v>59042</v>
       </c>
       <c r="E51" s="1">
-        <v>61304</v>
+        <v>64340</v>
       </c>
       <c r="F51" s="1">
-        <v>70545</v>
+        <v>74095</v>
       </c>
       <c r="G51" s="1">
-        <v>92894</v>
+        <v>97568</v>
       </c>
       <c r="H51" s="1">
-        <v>290818</v>
+        <v>305450</v>
       </c>
       <c r="I51" s="1">
         <v>149631</v>
@@ -6285,25 +6283,25 @@
         <v>53</v>
       </c>
       <c r="B52" s="1">
-        <v>261844</v>
+        <v>269804</v>
       </c>
       <c r="C52" s="1">
         <v>35893</v>
       </c>
       <c r="D52" s="1">
-        <v>61000</v>
+        <v>62854</v>
       </c>
       <c r="E52" s="1">
-        <v>68516</v>
+        <v>71910</v>
       </c>
       <c r="F52" s="1">
-        <v>78845</v>
+        <v>82812</v>
       </c>
       <c r="G52" s="1">
-        <v>103827</v>
+        <v>109051</v>
       </c>
       <c r="H52" s="1">
-        <v>325028</v>
+        <v>341381</v>
       </c>
       <c r="I52" s="1">
         <v>154791</v>
@@ -6314,25 +6312,25 @@
         <v>54</v>
       </c>
       <c r="B53" s="1">
-        <v>275019</v>
+        <v>283379</v>
       </c>
       <c r="C53" s="1">
         <v>35893</v>
       </c>
       <c r="D53" s="1">
-        <v>64700</v>
+        <v>66667</v>
       </c>
       <c r="E53" s="1">
-        <v>75729</v>
+        <v>79479</v>
       </c>
       <c r="F53" s="1">
-        <v>87145</v>
+        <v>91529</v>
       </c>
       <c r="G53" s="1">
-        <v>114753</v>
+        <v>120527</v>
       </c>
       <c r="H53" s="1">
-        <v>359237</v>
+        <v>377312</v>
       </c>
       <c r="I53" s="1">
         <v>159951</v>
@@ -6343,25 +6341,25 @@
         <v>55</v>
       </c>
       <c r="B54" s="1">
-        <v>292225</v>
+        <v>301109</v>
       </c>
       <c r="C54" s="1">
         <v>35893</v>
       </c>
       <c r="D54" s="1">
-        <v>68400</v>
+        <v>70479</v>
       </c>
       <c r="E54" s="1">
-        <v>82941</v>
+        <v>87049</v>
       </c>
       <c r="F54" s="1">
-        <v>95445</v>
+        <v>100247</v>
       </c>
       <c r="G54" s="1">
-        <v>125680</v>
+        <v>132003</v>
       </c>
       <c r="H54" s="1">
-        <v>393455</v>
+        <v>413251</v>
       </c>
       <c r="I54" s="1">
         <v>165110</v>
@@ -6373,7 +6371,7 @@
       </c>
       <c r="B55" s="2">
         <f t="shared" ref="B55:I55" si="0">B54*(1.05)</f>
-        <v>306836.25</v>
+        <v>316164.45</v>
       </c>
       <c r="C55" s="2">
         <f t="shared" si="0"/>
@@ -6381,23 +6379,23 @@
       </c>
       <c r="D55" s="2">
         <f t="shared" si="0"/>
-        <v>71820</v>
+        <v>74002.95</v>
       </c>
       <c r="E55" s="2">
         <f t="shared" si="0"/>
-        <v>87088.05</v>
+        <v>91401.45</v>
       </c>
       <c r="F55" s="2">
         <f t="shared" si="0"/>
-        <v>100217.25</v>
+        <v>105259.35</v>
       </c>
       <c r="G55" s="2">
         <f t="shared" si="0"/>
-        <v>131964</v>
+        <v>138603.15</v>
       </c>
       <c r="H55" s="2">
         <f t="shared" si="0"/>
-        <v>413127.75</v>
+        <v>433913.55000000005</v>
       </c>
       <c r="I55" s="2">
         <f t="shared" si="0"/>
@@ -6449,22 +6447,22 @@
         <v>32149</v>
       </c>
       <c r="C2" s="1">
-        <v>2596</v>
+        <v>2729</v>
       </c>
       <c r="D2" s="1">
-        <v>3146</v>
+        <v>3306</v>
       </c>
       <c r="E2" s="1">
-        <v>4143</v>
+        <v>4355</v>
       </c>
       <c r="F2" s="1">
-        <v>8969</v>
+        <v>9427</v>
       </c>
       <c r="G2" s="1">
-        <v>3461</v>
+        <v>3638</v>
       </c>
       <c r="H2" s="1">
-        <v>13413</v>
+        <v>14098</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -6475,22 +6473,22 @@
         <v>34363</v>
       </c>
       <c r="C3" s="1">
-        <v>3461</v>
+        <v>3638</v>
       </c>
       <c r="D3" s="1">
-        <v>4194</v>
+        <v>4408</v>
       </c>
       <c r="E3" s="1">
-        <v>5528</v>
+        <v>5810</v>
       </c>
       <c r="F3" s="1">
-        <v>11962</v>
+        <v>12573</v>
       </c>
       <c r="G3" s="1">
-        <v>4622</v>
+        <v>4858</v>
       </c>
       <c r="H3" s="1">
-        <v>17896</v>
+        <v>18811</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6501,22 +6499,22 @@
         <v>36583</v>
       </c>
       <c r="C4" s="1">
-        <v>4327</v>
+        <v>4548</v>
       </c>
       <c r="D4" s="1">
-        <v>5243</v>
+        <v>5511</v>
       </c>
       <c r="E4" s="1">
-        <v>6912</v>
+        <v>7265</v>
       </c>
       <c r="F4" s="1">
-        <v>14954</v>
+        <v>15718</v>
       </c>
       <c r="G4" s="1">
-        <v>5782</v>
+        <v>6078</v>
       </c>
       <c r="H4" s="1">
-        <v>22380</v>
+        <v>23523</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6527,22 +6525,22 @@
         <v>38797</v>
       </c>
       <c r="C5" s="1">
-        <v>5192</v>
+        <v>5457</v>
       </c>
       <c r="D5" s="1">
-        <v>6291</v>
+        <v>6613</v>
       </c>
       <c r="E5" s="1">
-        <v>8297</v>
+        <v>8721</v>
       </c>
       <c r="F5" s="1">
-        <v>17947</v>
+        <v>18864</v>
       </c>
       <c r="G5" s="1">
-        <v>6943</v>
+        <v>7297</v>
       </c>
       <c r="H5" s="1">
-        <v>26863</v>
+        <v>28235</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6553,22 +6551,22 @@
         <v>41011</v>
       </c>
       <c r="C6" s="1">
-        <v>6057</v>
+        <v>6367</v>
       </c>
       <c r="D6" s="1">
-        <v>7340</v>
+        <v>7715</v>
       </c>
       <c r="E6" s="1">
-        <v>9681</v>
+        <v>10176</v>
       </c>
       <c r="F6" s="1">
-        <v>20940</v>
+        <v>22010</v>
       </c>
       <c r="G6" s="1">
-        <v>8103</v>
+        <v>8517</v>
       </c>
       <c r="H6" s="1">
-        <v>31346</v>
+        <v>32947</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -6579,22 +6577,22 @@
         <v>43225</v>
       </c>
       <c r="C7" s="1">
-        <v>6922</v>
+        <v>7276</v>
       </c>
       <c r="D7" s="1">
-        <v>8388</v>
+        <v>8817</v>
       </c>
       <c r="E7" s="1">
-        <v>11066</v>
+        <v>11631</v>
       </c>
       <c r="F7" s="1">
-        <v>23933</v>
+        <v>25156</v>
       </c>
       <c r="G7" s="1">
-        <v>9264</v>
+        <v>9737</v>
       </c>
       <c r="H7" s="1">
-        <v>35830</v>
+        <v>37660</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -6605,22 +6603,22 @@
         <v>45439</v>
       </c>
       <c r="C8" s="1">
-        <v>7788</v>
+        <v>8186</v>
       </c>
       <c r="D8" s="1">
-        <v>9437</v>
+        <v>9919</v>
       </c>
       <c r="E8" s="1">
-        <v>12450</v>
+        <v>13086</v>
       </c>
       <c r="F8" s="1">
-        <v>26926</v>
+        <v>28302</v>
       </c>
       <c r="G8" s="1">
-        <v>10424</v>
+        <v>10957</v>
       </c>
       <c r="H8" s="1">
-        <v>40313</v>
+        <v>42372</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -6631,22 +6629,22 @@
         <v>34363</v>
       </c>
       <c r="C9" s="1">
-        <v>3461</v>
+        <v>3638</v>
       </c>
       <c r="D9" s="1">
-        <v>4194</v>
+        <v>4408</v>
       </c>
       <c r="E9" s="1">
-        <v>5528</v>
+        <v>5810</v>
       </c>
       <c r="F9" s="1">
-        <v>11962</v>
+        <v>12573</v>
       </c>
       <c r="G9" s="1">
-        <v>4622</v>
+        <v>4858</v>
       </c>
       <c r="H9" s="1">
-        <v>17896</v>
+        <v>18811</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -6657,22 +6655,22 @@
         <v>36583</v>
       </c>
       <c r="C10" s="1">
-        <v>4622</v>
+        <v>4858</v>
       </c>
       <c r="D10" s="1">
-        <v>5589</v>
+        <v>5874</v>
       </c>
       <c r="E10" s="1">
-        <v>7381</v>
+        <v>7758</v>
       </c>
       <c r="F10" s="1">
-        <v>15942</v>
+        <v>16756</v>
       </c>
       <c r="G10" s="1">
-        <v>6159</v>
+        <v>6474</v>
       </c>
       <c r="H10" s="1">
-        <v>23858</v>
+        <v>25077</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -6683,22 +6681,22 @@
         <v>38797</v>
       </c>
       <c r="C11" s="1">
-        <v>5772</v>
+        <v>6067</v>
       </c>
       <c r="D11" s="1">
-        <v>6983</v>
+        <v>7340</v>
       </c>
       <c r="E11" s="1">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="F11" s="1">
-        <v>19922</v>
+        <v>20940</v>
       </c>
       <c r="G11" s="1">
-        <v>7696</v>
+        <v>8089</v>
       </c>
       <c r="H11" s="1">
-        <v>29819</v>
+        <v>31342</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -6709,22 +6707,22 @@
         <v>41011</v>
       </c>
       <c r="C12" s="1">
-        <v>6922</v>
+        <v>7276</v>
       </c>
       <c r="D12" s="1">
-        <v>8378</v>
+        <v>8806</v>
       </c>
       <c r="E12" s="1">
-        <v>11086</v>
+        <v>11652</v>
       </c>
       <c r="F12" s="1">
-        <v>23903</v>
+        <v>25124</v>
       </c>
       <c r="G12" s="1">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="H12" s="1">
-        <v>35781</v>
+        <v>37608</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -6735,22 +6733,22 @@
         <v>43225</v>
       </c>
       <c r="C13" s="1">
-        <v>8083</v>
+        <v>8496</v>
       </c>
       <c r="D13" s="1">
-        <v>9773</v>
+        <v>10272</v>
       </c>
       <c r="E13" s="1">
-        <v>12939</v>
+        <v>13600</v>
       </c>
       <c r="F13" s="1">
-        <v>27883</v>
+        <v>29307</v>
       </c>
       <c r="G13" s="1">
-        <v>10770</v>
+        <v>11321</v>
       </c>
       <c r="H13" s="1">
-        <v>41742</v>
+        <v>43874</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -6761,22 +6759,22 @@
         <v>45439</v>
       </c>
       <c r="C14" s="1">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="D14" s="1">
-        <v>11167</v>
+        <v>11738</v>
       </c>
       <c r="E14" s="1">
-        <v>14792</v>
+        <v>15547</v>
       </c>
       <c r="F14" s="1">
-        <v>31863</v>
+        <v>33491</v>
       </c>
       <c r="G14" s="1">
-        <v>12308</v>
+        <v>12936</v>
       </c>
       <c r="H14" s="1">
-        <v>47703</v>
+        <v>50140</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -6787,22 +6785,22 @@
         <v>47653</v>
       </c>
       <c r="C15" s="1">
-        <v>10384</v>
+        <v>10914</v>
       </c>
       <c r="D15" s="1">
-        <v>12562</v>
+        <v>13204</v>
       </c>
       <c r="E15" s="1">
-        <v>16644</v>
+        <v>17495</v>
       </c>
       <c r="F15" s="1">
-        <v>35844</v>
+        <v>37675</v>
       </c>
       <c r="G15" s="1">
-        <v>13845</v>
+        <v>14552</v>
       </c>
       <c r="H15" s="1">
-        <v>53665</v>
+        <v>56406</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -6813,22 +6811,22 @@
         <v>36583</v>
       </c>
       <c r="C16" s="1">
-        <v>4327</v>
+        <v>4548</v>
       </c>
       <c r="D16" s="1">
-        <v>5243</v>
+        <v>5511</v>
       </c>
       <c r="E16" s="1">
-        <v>6912</v>
+        <v>7265</v>
       </c>
       <c r="F16" s="1">
-        <v>14954</v>
+        <v>15718</v>
       </c>
       <c r="G16" s="1">
-        <v>5782</v>
+        <v>6078</v>
       </c>
       <c r="H16" s="1">
-        <v>22380</v>
+        <v>23523</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6839,22 +6837,22 @@
         <v>38797</v>
       </c>
       <c r="C17" s="1">
-        <v>5772</v>
+        <v>6067</v>
       </c>
       <c r="D17" s="1">
-        <v>6983</v>
+        <v>7340</v>
       </c>
       <c r="E17" s="1">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="F17" s="1">
-        <v>19922</v>
+        <v>20940</v>
       </c>
       <c r="G17" s="1">
-        <v>7696</v>
+        <v>8089</v>
       </c>
       <c r="H17" s="1">
-        <v>29819</v>
+        <v>31342</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -6865,22 +6863,22 @@
         <v>41011</v>
       </c>
       <c r="C18" s="1">
-        <v>7207</v>
+        <v>7576</v>
       </c>
       <c r="D18" s="1">
-        <v>8724</v>
+        <v>9170</v>
       </c>
       <c r="E18" s="1">
-        <v>11554</v>
+        <v>12145</v>
       </c>
       <c r="F18" s="1">
-        <v>24890</v>
+        <v>26162</v>
       </c>
       <c r="G18" s="1">
-        <v>9610</v>
+        <v>10101</v>
       </c>
       <c r="H18" s="1">
-        <v>37259</v>
+        <v>39162</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6891,22 +6889,22 @@
         <v>43225</v>
       </c>
       <c r="C19" s="1">
-        <v>8653</v>
+        <v>9095</v>
       </c>
       <c r="D19" s="1">
-        <v>10465</v>
+        <v>11000</v>
       </c>
       <c r="E19" s="1">
-        <v>13875</v>
+        <v>14584</v>
       </c>
       <c r="F19" s="1">
-        <v>29960</v>
+        <v>31490</v>
       </c>
       <c r="G19" s="1">
-        <v>11524</v>
+        <v>12112</v>
       </c>
       <c r="H19" s="1">
-        <v>44698</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -6917,22 +6915,22 @@
         <v>45439</v>
       </c>
       <c r="C20" s="1">
-        <v>10099</v>
+        <v>10614</v>
       </c>
       <c r="D20" s="1">
-        <v>12206</v>
+        <v>12829</v>
       </c>
       <c r="E20" s="1">
-        <v>16196</v>
+        <v>17024</v>
       </c>
       <c r="F20" s="1">
-        <v>35029</v>
+        <v>36819</v>
       </c>
       <c r="G20" s="1">
-        <v>13438</v>
+        <v>14124</v>
       </c>
       <c r="H20" s="1">
-        <v>52138</v>
+        <v>54801</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -6943,22 +6941,22 @@
         <v>47653</v>
       </c>
       <c r="C21" s="1">
-        <v>11544</v>
+        <v>12134</v>
       </c>
       <c r="D21" s="1">
-        <v>13947</v>
+        <v>14659</v>
       </c>
       <c r="E21" s="1">
-        <v>18517</v>
+        <v>19463</v>
       </c>
       <c r="F21" s="1">
-        <v>40099</v>
+        <v>42147</v>
       </c>
       <c r="G21" s="1">
-        <v>15351</v>
+        <v>16136</v>
       </c>
       <c r="H21" s="1">
-        <v>59577</v>
+        <v>62621</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6969,22 +6967,22 @@
         <v>49867</v>
       </c>
       <c r="C22" s="1">
-        <v>12990</v>
+        <v>13653</v>
       </c>
       <c r="D22" s="1">
-        <v>15687</v>
+        <v>16489</v>
       </c>
       <c r="E22" s="1">
-        <v>20838</v>
+        <v>21903</v>
       </c>
       <c r="F22" s="1">
-        <v>45169</v>
+        <v>47476</v>
       </c>
       <c r="G22" s="1">
-        <v>17265</v>
+        <v>18147</v>
       </c>
       <c r="H22" s="1">
-        <v>67017</v>
+        <v>70440</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6995,22 +6993,22 @@
         <v>38797</v>
       </c>
       <c r="C23" s="1">
-        <v>5192</v>
+        <v>5457</v>
       </c>
       <c r="D23" s="1">
-        <v>6291</v>
+        <v>6613</v>
       </c>
       <c r="E23" s="1">
-        <v>8297</v>
+        <v>8721</v>
       </c>
       <c r="F23" s="1">
-        <v>17947</v>
+        <v>18864</v>
       </c>
       <c r="G23" s="1">
-        <v>6943</v>
+        <v>7297</v>
       </c>
       <c r="H23" s="1">
-        <v>26863</v>
+        <v>28235</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -7021,22 +7019,22 @@
         <v>41011</v>
       </c>
       <c r="C24" s="1">
-        <v>6922</v>
+        <v>7276</v>
       </c>
       <c r="D24" s="1">
-        <v>8378</v>
+        <v>8806</v>
       </c>
       <c r="E24" s="1">
-        <v>11086</v>
+        <v>11652</v>
       </c>
       <c r="F24" s="1">
-        <v>23903</v>
+        <v>25124</v>
       </c>
       <c r="G24" s="1">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="H24" s="1">
-        <v>35781</v>
+        <v>37608</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -7047,22 +7045,22 @@
         <v>43225</v>
       </c>
       <c r="C25" s="1">
-        <v>8653</v>
+        <v>9095</v>
       </c>
       <c r="D25" s="1">
-        <v>10465</v>
+        <v>11000</v>
       </c>
       <c r="E25" s="1">
-        <v>13875</v>
+        <v>14584</v>
       </c>
       <c r="F25" s="1">
-        <v>29960</v>
+        <v>31490</v>
       </c>
       <c r="G25" s="1">
-        <v>11524</v>
+        <v>12112</v>
       </c>
       <c r="H25" s="1">
-        <v>44698</v>
+        <v>46982</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -7073,22 +7071,22 @@
         <v>45439</v>
       </c>
       <c r="C26" s="1">
-        <v>10394</v>
+        <v>10925</v>
       </c>
       <c r="D26" s="1">
-        <v>12552</v>
+        <v>13193</v>
       </c>
       <c r="E26" s="1">
-        <v>16665</v>
+        <v>17516</v>
       </c>
       <c r="F26" s="1">
-        <v>36017</v>
+        <v>37857</v>
       </c>
       <c r="G26" s="1">
-        <v>13814</v>
+        <v>14520</v>
       </c>
       <c r="H26" s="1">
-        <v>53616</v>
+        <v>56355</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -7099,22 +7097,22 @@
         <v>47653</v>
       </c>
       <c r="C27" s="1">
-        <v>12124</v>
+        <v>12744</v>
       </c>
       <c r="D27" s="1">
-        <v>14639</v>
+        <v>15387</v>
       </c>
       <c r="E27" s="1">
-        <v>19454</v>
+        <v>20448</v>
       </c>
       <c r="F27" s="1">
-        <v>42074</v>
+        <v>44223</v>
       </c>
       <c r="G27" s="1">
-        <v>16105</v>
+        <v>16927</v>
       </c>
       <c r="H27" s="1">
-        <v>62534</v>
+        <v>65728</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -7125,22 +7123,22 @@
         <v>49867</v>
       </c>
       <c r="C28" s="1">
-        <v>13855</v>
+        <v>14563</v>
       </c>
       <c r="D28" s="1">
-        <v>16726</v>
+        <v>17580</v>
       </c>
       <c r="E28" s="1">
-        <v>22243</v>
+        <v>23380</v>
       </c>
       <c r="F28" s="1">
-        <v>48131</v>
+        <v>50590</v>
       </c>
       <c r="G28" s="1">
-        <v>18395</v>
+        <v>19335</v>
       </c>
       <c r="H28" s="1">
-        <v>71451</v>
+        <v>75101</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -7151,22 +7149,22 @@
         <v>52081</v>
       </c>
       <c r="C29" s="1">
-        <v>15586</v>
+        <v>16382</v>
       </c>
       <c r="D29" s="1">
-        <v>18813</v>
+        <v>19774</v>
       </c>
       <c r="E29" s="1">
-        <v>25033</v>
+        <v>26311</v>
       </c>
       <c r="F29" s="1">
-        <v>54188</v>
+        <v>56956</v>
       </c>
       <c r="G29" s="1">
-        <v>20686</v>
+        <v>21742</v>
       </c>
       <c r="H29" s="1">
-        <v>80369</v>
+        <v>84474</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7177,22 +7175,22 @@
         <v>41011</v>
       </c>
       <c r="C30" s="1">
-        <v>6057</v>
+        <v>6367</v>
       </c>
       <c r="D30" s="1">
-        <v>7340</v>
+        <v>7715</v>
       </c>
       <c r="E30" s="1">
-        <v>9681</v>
+        <v>10176</v>
       </c>
       <c r="F30" s="1">
-        <v>20940</v>
+        <v>22010</v>
       </c>
       <c r="G30" s="1">
-        <v>8103</v>
+        <v>8517</v>
       </c>
       <c r="H30" s="1">
-        <v>31346</v>
+        <v>32947</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -7203,22 +7201,22 @@
         <v>43225</v>
       </c>
       <c r="C31" s="1">
-        <v>8083</v>
+        <v>8496</v>
       </c>
       <c r="D31" s="1">
-        <v>9773</v>
+        <v>10272</v>
       </c>
       <c r="E31" s="1">
-        <v>12939</v>
+        <v>13600</v>
       </c>
       <c r="F31" s="1">
-        <v>27883</v>
+        <v>29307</v>
       </c>
       <c r="G31" s="1">
-        <v>10770</v>
+        <v>11321</v>
       </c>
       <c r="H31" s="1">
-        <v>41742</v>
+        <v>43874</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -7229,22 +7227,22 @@
         <v>47653</v>
       </c>
       <c r="C32" s="1">
-        <v>12124</v>
+        <v>12744</v>
       </c>
       <c r="D32" s="1">
-        <v>14639</v>
+        <v>15387</v>
       </c>
       <c r="E32" s="1">
-        <v>19454</v>
+        <v>20448</v>
       </c>
       <c r="F32" s="1">
-        <v>42074</v>
+        <v>44223</v>
       </c>
       <c r="G32" s="1">
-        <v>16105</v>
+        <v>16927</v>
       </c>
       <c r="H32" s="1">
-        <v>62534</v>
+        <v>65728</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -7255,22 +7253,22 @@
         <v>49867</v>
       </c>
       <c r="C33" s="1">
-        <v>14140</v>
+        <v>14862</v>
       </c>
       <c r="D33" s="1">
-        <v>17072</v>
+        <v>17944</v>
       </c>
       <c r="E33" s="1">
-        <v>22712</v>
+        <v>23872</v>
       </c>
       <c r="F33" s="1">
-        <v>49119</v>
+        <v>51628</v>
       </c>
       <c r="G33" s="1">
-        <v>18772</v>
+        <v>19731</v>
       </c>
       <c r="H33" s="1">
-        <v>72930</v>
+        <v>76655</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -7281,22 +7279,22 @@
         <v>52081</v>
       </c>
       <c r="C34" s="1">
-        <v>16156</v>
+        <v>16981</v>
       </c>
       <c r="D34" s="1">
-        <v>19505</v>
+        <v>20501</v>
       </c>
       <c r="E34" s="1">
-        <v>25969</v>
+        <v>27296</v>
       </c>
       <c r="F34" s="1">
-        <v>56163</v>
+        <v>59032</v>
       </c>
       <c r="G34" s="1">
-        <v>21439</v>
+        <v>22534</v>
       </c>
       <c r="H34" s="1">
-        <v>83325</v>
+        <v>87582</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -7307,22 +7305,22 @@
         <v>54295</v>
       </c>
       <c r="C35" s="1">
-        <v>18171</v>
+        <v>19100</v>
       </c>
       <c r="D35" s="1">
-        <v>21938</v>
+        <v>23059</v>
       </c>
       <c r="E35" s="1">
-        <v>29227</v>
+        <v>30720</v>
       </c>
       <c r="F35" s="1">
-        <v>63208</v>
+        <v>66436</v>
       </c>
       <c r="G35" s="1">
-        <v>24106</v>
+        <v>25338</v>
       </c>
       <c r="H35" s="1">
-        <v>93721</v>
+        <v>98508</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -7333,22 +7331,22 @@
         <v>43225</v>
       </c>
       <c r="C36" s="1">
-        <v>6922</v>
+        <v>7276</v>
       </c>
       <c r="D36" s="1">
-        <v>8388</v>
+        <v>8817</v>
       </c>
       <c r="E36" s="1">
-        <v>11066</v>
+        <v>11631</v>
       </c>
       <c r="F36" s="1">
-        <v>23933</v>
+        <v>25156</v>
       </c>
       <c r="G36" s="1">
-        <v>9264</v>
+        <v>9737</v>
       </c>
       <c r="H36" s="1">
-        <v>35830</v>
+        <v>37660</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -7359,22 +7357,22 @@
         <v>45439</v>
       </c>
       <c r="C37" s="1">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="D37" s="1">
-        <v>11167</v>
+        <v>11738</v>
       </c>
       <c r="E37" s="1">
-        <v>14792</v>
+        <v>15547</v>
       </c>
       <c r="F37" s="1">
-        <v>31863</v>
+        <v>33491</v>
       </c>
       <c r="G37" s="1">
-        <v>12308</v>
+        <v>12936</v>
       </c>
       <c r="H37" s="1">
-        <v>47703</v>
+        <v>50140</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -7385,22 +7383,22 @@
         <v>47653</v>
       </c>
       <c r="C38" s="1">
-        <v>11544</v>
+        <v>12134</v>
       </c>
       <c r="D38" s="1">
-        <v>13947</v>
+        <v>14659</v>
       </c>
       <c r="E38" s="1">
-        <v>18517</v>
+        <v>19463</v>
       </c>
       <c r="F38" s="1">
-        <v>40099</v>
+        <v>42147</v>
       </c>
       <c r="G38" s="1">
-        <v>15351</v>
+        <v>16136</v>
       </c>
       <c r="H38" s="1">
-        <v>59577</v>
+        <v>62621</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -7411,22 +7409,22 @@
         <v>49867</v>
       </c>
       <c r="C39" s="1">
-        <v>13855</v>
+        <v>14563</v>
       </c>
       <c r="D39" s="1">
-        <v>16726</v>
+        <v>17580</v>
       </c>
       <c r="E39" s="1">
-        <v>22243</v>
+        <v>23380</v>
       </c>
       <c r="F39" s="1">
-        <v>48131</v>
+        <v>50590</v>
       </c>
       <c r="G39" s="1">
-        <v>18395</v>
+        <v>19335</v>
       </c>
       <c r="H39" s="1">
-        <v>71451</v>
+        <v>75101</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -7437,22 +7435,22 @@
         <v>52081</v>
       </c>
       <c r="C40" s="1">
-        <v>16156</v>
+        <v>16981</v>
       </c>
       <c r="D40" s="1">
-        <v>19505</v>
+        <v>20501</v>
       </c>
       <c r="E40" s="1">
-        <v>25969</v>
+        <v>27296</v>
       </c>
       <c r="F40" s="1">
-        <v>56163</v>
+        <v>59032</v>
       </c>
       <c r="G40" s="1">
-        <v>21439</v>
+        <v>22534</v>
       </c>
       <c r="H40" s="1">
-        <v>83325</v>
+        <v>87582</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -7463,22 +7461,22 @@
         <v>54295</v>
       </c>
       <c r="C41" s="1">
-        <v>18467</v>
+        <v>19410</v>
       </c>
       <c r="D41" s="1">
-        <v>22284</v>
+        <v>23422</v>
       </c>
       <c r="E41" s="1">
-        <v>29695</v>
+        <v>31212</v>
       </c>
       <c r="F41" s="1">
-        <v>64195</v>
+        <v>67474</v>
       </c>
       <c r="G41" s="1">
-        <v>24483</v>
+        <v>25734</v>
       </c>
       <c r="H41" s="1">
-        <v>95199</v>
+        <v>100062</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -7489,22 +7487,22 @@
         <v>56515</v>
       </c>
       <c r="C42" s="1">
-        <v>20777</v>
+        <v>21839</v>
       </c>
       <c r="D42" s="1">
-        <v>25063</v>
+        <v>26343</v>
       </c>
       <c r="E42" s="1">
-        <v>33411</v>
+        <v>35117</v>
       </c>
       <c r="F42" s="1">
-        <v>72227</v>
+        <v>75917</v>
       </c>
       <c r="G42" s="1">
-        <v>27527</v>
+        <v>28933</v>
       </c>
       <c r="H42" s="1">
-        <v>107073</v>
+        <v>112543</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -7515,22 +7513,22 @@
         <v>45439</v>
       </c>
       <c r="C43" s="1">
-        <v>7788</v>
+        <v>8186</v>
       </c>
       <c r="D43" s="1">
-        <v>9437</v>
+        <v>9919</v>
       </c>
       <c r="E43" s="1">
-        <v>12450</v>
+        <v>13086</v>
       </c>
       <c r="F43" s="1">
-        <v>26926</v>
+        <v>28302</v>
       </c>
       <c r="G43" s="1">
-        <v>10424</v>
+        <v>10957</v>
       </c>
       <c r="H43" s="1">
-        <v>40313</v>
+        <v>42372</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -7541,22 +7539,22 @@
         <v>47653</v>
       </c>
       <c r="C44" s="1">
-        <v>10384</v>
+        <v>10914</v>
       </c>
       <c r="D44" s="1">
-        <v>12562</v>
+        <v>13204</v>
       </c>
       <c r="E44" s="1">
-        <v>16644</v>
+        <v>17495</v>
       </c>
       <c r="F44" s="1">
-        <v>35844</v>
+        <v>37675</v>
       </c>
       <c r="G44" s="1">
-        <v>13845</v>
+        <v>14552</v>
       </c>
       <c r="H44" s="1">
-        <v>53665</v>
+        <v>56406</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -7567,22 +7565,22 @@
         <v>49867</v>
       </c>
       <c r="C45" s="1">
-        <v>12990</v>
+        <v>13653</v>
       </c>
       <c r="D45" s="1">
-        <v>15687</v>
+        <v>16489</v>
       </c>
       <c r="E45" s="1">
-        <v>20838</v>
+        <v>21903</v>
       </c>
       <c r="F45" s="1">
-        <v>45169</v>
+        <v>47476</v>
       </c>
       <c r="G45" s="1">
-        <v>17265</v>
+        <v>18147</v>
       </c>
       <c r="H45" s="1">
-        <v>67017</v>
+        <v>70440</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -7593,22 +7591,22 @@
         <v>52081</v>
       </c>
       <c r="C46" s="1">
-        <v>15586</v>
+        <v>16382</v>
       </c>
       <c r="D46" s="1">
-        <v>18813</v>
+        <v>19774</v>
       </c>
       <c r="E46" s="1">
-        <v>25033</v>
+        <v>26311</v>
       </c>
       <c r="F46" s="1">
-        <v>54188</v>
+        <v>56956</v>
       </c>
       <c r="G46" s="1">
-        <v>20686</v>
+        <v>21742</v>
       </c>
       <c r="H46" s="1">
-        <v>80369</v>
+        <v>84474</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -7619,22 +7617,22 @@
         <v>54295</v>
       </c>
       <c r="C47" s="1">
-        <v>18171</v>
+        <v>19100</v>
       </c>
       <c r="D47" s="1">
-        <v>21938</v>
+        <v>23059</v>
       </c>
       <c r="E47" s="1">
-        <v>29227</v>
+        <v>30720</v>
       </c>
       <c r="F47" s="1">
-        <v>63208</v>
+        <v>66436</v>
       </c>
       <c r="G47" s="1">
-        <v>24106</v>
+        <v>25338</v>
       </c>
       <c r="H47" s="1">
-        <v>93721</v>
+        <v>98508</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -7645,22 +7643,22 @@
         <v>56515</v>
       </c>
       <c r="C48" s="1">
-        <v>20777</v>
+        <v>21839</v>
       </c>
       <c r="D48" s="1">
-        <v>25063</v>
+        <v>26343</v>
       </c>
       <c r="E48" s="1">
-        <v>33411</v>
+        <v>35117</v>
       </c>
       <c r="F48" s="1">
-        <v>72227</v>
+        <v>75917</v>
       </c>
       <c r="G48" s="1">
-        <v>27527</v>
+        <v>28933</v>
       </c>
       <c r="H48" s="1">
-        <v>107073</v>
+        <v>112543</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -7671,22 +7669,22 @@
         <v>58729</v>
       </c>
       <c r="C49" s="1">
-        <v>23383</v>
+        <v>24578</v>
       </c>
       <c r="D49" s="1">
-        <v>27659</v>
+        <v>29072</v>
       </c>
       <c r="E49" s="1">
-        <v>37595</v>
+        <v>39515</v>
       </c>
       <c r="F49" s="1">
-        <v>80707</v>
+        <v>84830</v>
       </c>
       <c r="G49" s="1">
-        <v>30947</v>
+        <v>32528</v>
       </c>
       <c r="H49" s="1">
-        <v>120425</v>
+        <v>126577</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -7697,22 +7695,22 @@
         <v>47653</v>
       </c>
       <c r="C50" s="1">
-        <v>8653</v>
+        <v>9095</v>
       </c>
       <c r="D50" s="1">
-        <v>10485</v>
+        <v>11021</v>
       </c>
       <c r="E50" s="1">
-        <v>13845</v>
+        <v>14552</v>
       </c>
       <c r="F50" s="1">
-        <v>29888</v>
+        <v>31415</v>
       </c>
       <c r="G50" s="1">
-        <v>11544</v>
+        <v>12134</v>
       </c>
       <c r="H50" s="1">
-        <v>44723</v>
+        <v>47007</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -7723,22 +7721,22 @@
         <v>49867</v>
       </c>
       <c r="C51" s="1">
-        <v>11544</v>
+        <v>12134</v>
       </c>
       <c r="D51" s="1">
-        <v>13977</v>
+        <v>14691</v>
       </c>
       <c r="E51" s="1">
-        <v>18456</v>
+        <v>19399</v>
       </c>
       <c r="F51" s="1">
-        <v>39855</v>
+        <v>41891</v>
       </c>
       <c r="G51" s="1">
-        <v>15392</v>
+        <v>16178</v>
       </c>
       <c r="H51" s="1">
-        <v>59639</v>
+        <v>62685</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -7749,22 +7747,22 @@
         <v>52081</v>
       </c>
       <c r="C52" s="1">
-        <v>14435</v>
+        <v>15173</v>
       </c>
       <c r="D52" s="1">
-        <v>17479</v>
+        <v>18372</v>
       </c>
       <c r="E52" s="1">
-        <v>23068</v>
+        <v>24246</v>
       </c>
       <c r="F52" s="1">
-        <v>49821</v>
+        <v>52366</v>
       </c>
       <c r="G52" s="1">
-        <v>19240</v>
+        <v>20223</v>
       </c>
       <c r="H52" s="1">
-        <v>74554</v>
+        <v>78363</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -7775,22 +7773,22 @@
         <v>54295</v>
       </c>
       <c r="C53" s="1">
-        <v>17326</v>
+        <v>18211</v>
       </c>
       <c r="D53" s="1">
-        <v>20971</v>
+        <v>22042</v>
       </c>
       <c r="E53" s="1">
-        <v>27679</v>
+        <v>29093</v>
       </c>
       <c r="F53" s="1">
-        <v>59787</v>
+        <v>62841</v>
       </c>
       <c r="G53" s="1">
-        <v>23088</v>
+        <v>24268</v>
       </c>
       <c r="H53" s="1">
-        <v>89470</v>
+        <v>94040</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -7801,22 +7799,22 @@
         <v>56515</v>
       </c>
       <c r="C54" s="1">
-        <v>20217</v>
+        <v>21250</v>
       </c>
       <c r="D54" s="1">
-        <v>24463</v>
+        <v>25712</v>
       </c>
       <c r="E54" s="1">
-        <v>32291</v>
+        <v>33940</v>
       </c>
       <c r="F54" s="1">
-        <v>69753</v>
+        <v>73316</v>
       </c>
       <c r="G54" s="1">
-        <v>26936</v>
+        <v>28312</v>
       </c>
       <c r="H54" s="1">
-        <v>104386</v>
+        <v>109718</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -7827,22 +7825,22 @@
         <v>58729</v>
       </c>
       <c r="C55" s="1">
-        <v>23109</v>
+        <v>24289</v>
       </c>
       <c r="D55" s="1">
-        <v>27954</v>
+        <v>29382</v>
       </c>
       <c r="E55" s="1">
-        <v>36903</v>
+        <v>38788</v>
       </c>
       <c r="F55" s="1">
-        <v>79720</v>
+        <v>83792</v>
       </c>
       <c r="G55" s="1">
-        <v>30784</v>
+        <v>32357</v>
       </c>
       <c r="H55" s="1">
-        <v>119301</v>
+        <v>125395</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -7853,22 +7851,22 @@
         <v>60943</v>
       </c>
       <c r="C56" s="1">
-        <v>26000</v>
+        <v>27328</v>
       </c>
       <c r="D56" s="1">
-        <v>31446</v>
+        <v>33052</v>
       </c>
       <c r="E56" s="1">
-        <v>41514</v>
+        <v>43635</v>
       </c>
       <c r="F56" s="1">
-        <v>89686</v>
+        <v>94267</v>
       </c>
       <c r="G56" s="1">
-        <v>34632</v>
+        <v>36401</v>
       </c>
       <c r="H56" s="1">
-        <v>134217</v>
+        <v>141073</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -7879,22 +7877,22 @@
         <v>49867</v>
       </c>
       <c r="C57" s="1">
-        <v>9528</v>
+        <v>10015</v>
       </c>
       <c r="D57" s="1">
-        <v>11534</v>
+        <v>12123</v>
       </c>
       <c r="E57" s="1">
-        <v>15229</v>
+        <v>16007</v>
       </c>
       <c r="F57" s="1">
-        <v>32881</v>
+        <v>34561</v>
       </c>
       <c r="G57" s="1">
-        <v>12694</v>
+        <v>13343</v>
       </c>
       <c r="H57" s="1">
-        <v>49194</v>
+        <v>51707</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -7905,22 +7903,22 @@
         <v>52081</v>
       </c>
       <c r="C58" s="1">
-        <v>12705</v>
+        <v>13354</v>
       </c>
       <c r="D58" s="1">
-        <v>15382</v>
+        <v>16168</v>
       </c>
       <c r="E58" s="1">
-        <v>20309</v>
+        <v>21347</v>
       </c>
       <c r="F58" s="1">
-        <v>43845</v>
+        <v>46085</v>
       </c>
       <c r="G58" s="1">
-        <v>16929</v>
+        <v>17794</v>
       </c>
       <c r="H58" s="1">
-        <v>65600</v>
+        <v>68951</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -7931,22 +7929,22 @@
         <v>54295</v>
       </c>
       <c r="C59" s="1">
-        <v>15881</v>
+        <v>16692</v>
       </c>
       <c r="D59" s="1">
-        <v>19230</v>
+        <v>20212</v>
       </c>
       <c r="E59" s="1">
-        <v>25389</v>
+        <v>26686</v>
       </c>
       <c r="F59" s="1">
-        <v>54809</v>
+        <v>57609</v>
       </c>
       <c r="G59" s="1">
-        <v>21164</v>
+        <v>22245</v>
       </c>
       <c r="H59" s="1">
-        <v>82006</v>
+        <v>86195</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -7957,22 +7955,22 @@
         <v>56515</v>
       </c>
       <c r="C60" s="1">
-        <v>19057</v>
+        <v>20030</v>
       </c>
       <c r="D60" s="1">
-        <v>23078</v>
+        <v>24257</v>
       </c>
       <c r="E60" s="1">
-        <v>30469</v>
+        <v>32025</v>
       </c>
       <c r="F60" s="1">
-        <v>65773</v>
+        <v>69133</v>
       </c>
       <c r="G60" s="1">
-        <v>25399</v>
+        <v>26697</v>
       </c>
       <c r="H60" s="1">
-        <v>98412</v>
+        <v>103439</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -7983,22 +7981,22 @@
         <v>58729</v>
       </c>
       <c r="C61" s="1">
-        <v>22233</v>
+        <v>23369</v>
       </c>
       <c r="D61" s="1">
-        <v>26926</v>
+        <v>28302</v>
       </c>
       <c r="E61" s="1">
-        <v>35549</v>
+        <v>37364</v>
       </c>
       <c r="F61" s="1">
-        <v>76737</v>
+        <v>80657</v>
       </c>
       <c r="G61" s="1">
-        <v>29634</v>
+        <v>31148</v>
       </c>
       <c r="H61" s="1">
-        <v>114818</v>
+        <v>120683</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -8009,22 +8007,22 @@
         <v>60943</v>
       </c>
       <c r="C62" s="1">
-        <v>25409</v>
+        <v>26707</v>
       </c>
       <c r="D62" s="1">
-        <v>30774</v>
+        <v>32346</v>
       </c>
       <c r="E62" s="1">
-        <v>40628</v>
+        <v>42704</v>
       </c>
       <c r="F62" s="1">
-        <v>87701</v>
+        <v>92181</v>
       </c>
       <c r="G62" s="1">
-        <v>33869</v>
+        <v>35599</v>
       </c>
       <c r="H62" s="1">
-        <v>131224</v>
+        <v>137927</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -8035,22 +8033,22 @@
         <v>63158</v>
       </c>
       <c r="C63" s="1">
-        <v>28585</v>
+        <v>30046</v>
       </c>
       <c r="D63" s="1">
-        <v>34622</v>
+        <v>36391</v>
       </c>
       <c r="E63" s="1">
-        <v>45708</v>
+        <v>48043</v>
       </c>
       <c r="F63" s="1">
-        <v>98665</v>
+        <v>103704</v>
       </c>
       <c r="G63" s="1">
-        <v>38104</v>
+        <v>40050</v>
       </c>
       <c r="H63" s="1">
-        <v>147630</v>
+        <v>155171</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -8061,22 +8059,22 @@
         <v>56515</v>
       </c>
       <c r="C64" s="1">
-        <v>12124</v>
+        <v>12744</v>
       </c>
       <c r="D64" s="1">
-        <v>14680</v>
+        <v>15429</v>
       </c>
       <c r="E64" s="1">
-        <v>19383</v>
+        <v>20373</v>
       </c>
       <c r="F64" s="1">
-        <v>41850</v>
+        <v>43988</v>
       </c>
       <c r="G64" s="1">
-        <v>16166</v>
+        <v>16992</v>
       </c>
       <c r="H64" s="1">
-        <v>62619</v>
+        <v>65818</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -8087,22 +8085,22 @@
         <v>58729</v>
       </c>
       <c r="C65" s="1">
-        <v>16166</v>
+        <v>16992</v>
       </c>
       <c r="D65" s="1">
-        <v>19576</v>
+        <v>20576</v>
       </c>
       <c r="E65" s="1">
-        <v>25847</v>
+        <v>27167</v>
       </c>
       <c r="F65" s="1">
-        <v>55797</v>
+        <v>58647</v>
       </c>
       <c r="G65" s="1">
-        <v>21551</v>
+        <v>22652</v>
       </c>
       <c r="H65" s="1">
-        <v>83484</v>
+        <v>87749</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -8113,22 +8111,22 @@
         <v>60943</v>
       </c>
       <c r="C66" s="1">
-        <v>20207</v>
+        <v>21240</v>
       </c>
       <c r="D66" s="1">
-        <v>24473</v>
+        <v>25723</v>
       </c>
       <c r="E66" s="1">
-        <v>32311</v>
+        <v>33962</v>
       </c>
       <c r="F66" s="1">
-        <v>69743</v>
+        <v>73306</v>
       </c>
       <c r="G66" s="1">
-        <v>26936</v>
+        <v>28312</v>
       </c>
       <c r="H66" s="1">
-        <v>104349</v>
+        <v>109679</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -8139,22 +8137,22 @@
         <v>63158</v>
       </c>
       <c r="C67" s="1">
-        <v>24249</v>
+        <v>25487</v>
       </c>
       <c r="D67" s="1">
-        <v>29369</v>
+        <v>30870</v>
       </c>
       <c r="E67" s="1">
-        <v>38776</v>
+        <v>40756</v>
       </c>
       <c r="F67" s="1">
-        <v>83690</v>
+        <v>87965</v>
       </c>
       <c r="G67" s="1">
-        <v>32322</v>
+        <v>33973</v>
       </c>
       <c r="H67" s="1">
-        <v>125214</v>
+        <v>131610</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -8165,22 +8163,22 @@
         <v>65372</v>
       </c>
       <c r="C68" s="1">
-        <v>28290</v>
+        <v>29735</v>
       </c>
       <c r="D68" s="1">
-        <v>34266</v>
+        <v>36016</v>
       </c>
       <c r="E68" s="1">
-        <v>45240</v>
+        <v>47551</v>
       </c>
       <c r="F68" s="1">
-        <v>97636</v>
+        <v>102624</v>
       </c>
       <c r="G68" s="1">
-        <v>37707</v>
+        <v>39633</v>
       </c>
       <c r="H68" s="1">
-        <v>138383</v>
+        <v>145452</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -8191,22 +8189,22 @@
         <v>67586</v>
       </c>
       <c r="C69" s="1">
-        <v>32332</v>
+        <v>33983</v>
       </c>
       <c r="D69" s="1">
-        <v>39162</v>
+        <v>41163</v>
       </c>
       <c r="E69" s="1">
-        <v>51704</v>
+        <v>54345</v>
       </c>
       <c r="F69" s="1">
-        <v>111583</v>
+        <v>117283</v>
       </c>
       <c r="G69" s="1">
-        <v>43092</v>
+        <v>45293</v>
       </c>
       <c r="H69" s="1">
-        <v>151552</v>
+        <v>159293</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -8217,22 +8215,22 @@
         <v>69800</v>
       </c>
       <c r="C70" s="1">
-        <v>36373</v>
+        <v>38231</v>
       </c>
       <c r="D70" s="1">
-        <v>44059</v>
+        <v>46310</v>
       </c>
       <c r="E70" s="1">
-        <v>58169</v>
+        <v>61140</v>
       </c>
       <c r="F70" s="1">
-        <v>125530</v>
+        <v>131942</v>
       </c>
       <c r="G70" s="1">
-        <v>48477</v>
+        <v>50953</v>
       </c>
       <c r="H70" s="1">
-        <v>172417</v>
+        <v>181224</v>
       </c>
     </row>
   </sheetData>
@@ -8279,25 +8277,25 @@
         <v>64</v>
       </c>
       <c r="B2">
-        <v>91406</v>
+        <v>94497</v>
       </c>
       <c r="C2">
-        <v>2596</v>
+        <v>2729</v>
       </c>
       <c r="D2">
-        <v>3146</v>
+        <v>3306</v>
       </c>
       <c r="E2">
-        <v>4143</v>
+        <v>4355</v>
       </c>
       <c r="F2">
-        <v>8969</v>
+        <v>9427</v>
       </c>
       <c r="G2">
-        <v>3461</v>
+        <v>3638</v>
       </c>
       <c r="H2">
-        <v>13413</v>
+        <v>14098</v>
       </c>
       <c r="I2">
         <v>24806</v>
@@ -8308,25 +8306,25 @@
         <v>65</v>
       </c>
       <c r="B3">
-        <v>96512</v>
+        <v>99777</v>
       </c>
       <c r="C3">
-        <v>3461</v>
+        <v>3638</v>
       </c>
       <c r="D3">
-        <v>4194</v>
+        <v>4408</v>
       </c>
       <c r="E3">
-        <v>5528</v>
+        <v>5810</v>
       </c>
       <c r="F3">
-        <v>11962</v>
+        <v>12573</v>
       </c>
       <c r="G3">
-        <v>4622</v>
+        <v>4858</v>
       </c>
       <c r="H3">
-        <v>17896</v>
+        <v>18811</v>
       </c>
       <c r="I3">
         <v>27907</v>
@@ -8337,25 +8335,25 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>101653</v>
+        <v>105091</v>
       </c>
       <c r="C4">
-        <v>4327</v>
+        <v>4548</v>
       </c>
       <c r="D4">
-        <v>5243</v>
+        <v>5511</v>
       </c>
       <c r="E4">
-        <v>6912</v>
+        <v>7265</v>
       </c>
       <c r="F4">
-        <v>14954</v>
+        <v>15718</v>
       </c>
       <c r="G4">
-        <v>5782</v>
+        <v>6078</v>
       </c>
       <c r="H4">
-        <v>22380</v>
+        <v>23523</v>
       </c>
       <c r="I4">
         <v>31008</v>
@@ -8366,25 +8364,25 @@
         <v>66</v>
       </c>
       <c r="B5">
-        <v>106774</v>
+        <v>110385</v>
       </c>
       <c r="C5">
-        <v>5192</v>
+        <v>5457</v>
       </c>
       <c r="D5">
-        <v>6291</v>
+        <v>6613</v>
       </c>
       <c r="E5">
-        <v>8297</v>
+        <v>8721</v>
       </c>
       <c r="F5">
-        <v>17947</v>
+        <v>18864</v>
       </c>
       <c r="G5">
-        <v>6943</v>
+        <v>7297</v>
       </c>
       <c r="H5">
-        <v>26863</v>
+        <v>28235</v>
       </c>
       <c r="I5">
         <v>34109</v>
@@ -8395,25 +8393,25 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>111908</v>
+        <v>115693</v>
       </c>
       <c r="C6">
-        <v>6057</v>
+        <v>6367</v>
       </c>
       <c r="D6">
-        <v>7340</v>
+        <v>7715</v>
       </c>
       <c r="E6">
-        <v>9681</v>
+        <v>10176</v>
       </c>
       <c r="F6">
-        <v>20940</v>
+        <v>22010</v>
       </c>
       <c r="G6">
-        <v>8103</v>
+        <v>8517</v>
       </c>
       <c r="H6">
-        <v>31346</v>
+        <v>32947</v>
       </c>
       <c r="I6">
         <v>37210</v>
@@ -8424,25 +8422,25 @@
         <v>67</v>
       </c>
       <c r="B7">
-        <v>117035</v>
+        <v>120993</v>
       </c>
       <c r="C7">
-        <v>6922</v>
+        <v>7276</v>
       </c>
       <c r="D7">
-        <v>8388</v>
+        <v>8817</v>
       </c>
       <c r="E7">
-        <v>11066</v>
+        <v>11631</v>
       </c>
       <c r="F7">
-        <v>23933</v>
+        <v>25156</v>
       </c>
       <c r="G7">
-        <v>9264</v>
+        <v>9737</v>
       </c>
       <c r="H7">
-        <v>35830</v>
+        <v>37660</v>
       </c>
       <c r="I7">
         <v>40310</v>
@@ -8453,25 +8451,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>122142</v>
+        <v>126273</v>
       </c>
       <c r="C8">
-        <v>7788</v>
+        <v>8186</v>
       </c>
       <c r="D8">
-        <v>9437</v>
+        <v>9919</v>
       </c>
       <c r="E8">
-        <v>12450</v>
+        <v>13086</v>
       </c>
       <c r="F8">
-        <v>26926</v>
+        <v>28302</v>
       </c>
       <c r="G8">
-        <v>10424</v>
+        <v>10957</v>
       </c>
       <c r="H8">
-        <v>40313</v>
+        <v>42372</v>
       </c>
       <c r="I8">
         <v>43411</v>
@@ -8482,25 +8480,25 @@
         <v>68</v>
       </c>
       <c r="B9">
-        <v>96526</v>
+        <v>99791</v>
       </c>
       <c r="C9">
-        <v>3461</v>
+        <v>3638</v>
       </c>
       <c r="D9">
-        <v>4194</v>
+        <v>4408</v>
       </c>
       <c r="E9">
-        <v>5528</v>
+        <v>5810</v>
       </c>
       <c r="F9">
-        <v>11962</v>
+        <v>12573</v>
       </c>
       <c r="G9">
-        <v>4622</v>
+        <v>4858</v>
       </c>
       <c r="H9">
-        <v>17896</v>
+        <v>18811</v>
       </c>
       <c r="I9">
         <v>27907</v>
@@ -8511,25 +8509,25 @@
         <v>69</v>
       </c>
       <c r="B10">
-        <v>101653</v>
+        <v>105091</v>
       </c>
       <c r="C10">
-        <v>4622</v>
+        <v>4858</v>
       </c>
       <c r="D10">
-        <v>5589</v>
+        <v>5874</v>
       </c>
       <c r="E10">
-        <v>7381</v>
+        <v>7758</v>
       </c>
       <c r="F10">
-        <v>15942</v>
+        <v>16756</v>
       </c>
       <c r="G10">
-        <v>6159</v>
+        <v>6474</v>
       </c>
       <c r="H10">
-        <v>23858</v>
+        <v>25077</v>
       </c>
       <c r="I10">
         <v>31008</v>
@@ -8540,25 +8538,25 @@
         <v>70</v>
       </c>
       <c r="B11">
-        <v>106774</v>
+        <v>110385</v>
       </c>
       <c r="C11">
-        <v>5772</v>
+        <v>6067</v>
       </c>
       <c r="D11">
-        <v>6983</v>
+        <v>7340</v>
       </c>
       <c r="E11">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="F11">
-        <v>19922</v>
+        <v>20940</v>
       </c>
       <c r="G11">
-        <v>7696</v>
+        <v>8089</v>
       </c>
       <c r="H11">
-        <v>29819</v>
+        <v>31342</v>
       </c>
       <c r="I11">
         <v>34109</v>
@@ -8569,25 +8567,25 @@
         <v>71</v>
       </c>
       <c r="B12">
-        <v>111894</v>
+        <v>115679</v>
       </c>
       <c r="C12">
-        <v>6922</v>
+        <v>7276</v>
       </c>
       <c r="D12">
-        <v>8378</v>
+        <v>8806</v>
       </c>
       <c r="E12">
-        <v>11086</v>
+        <v>11652</v>
       </c>
       <c r="F12">
-        <v>23903</v>
+        <v>25124</v>
       </c>
       <c r="G12">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="H12">
-        <v>35781</v>
+        <v>37608</v>
       </c>
       <c r="I12">
         <v>37210</v>
@@ -8598,25 +8596,25 @@
         <v>72</v>
       </c>
       <c r="B13">
-        <v>117035</v>
+        <v>120993</v>
       </c>
       <c r="C13">
-        <v>8083</v>
+        <v>8496</v>
       </c>
       <c r="D13">
-        <v>9773</v>
+        <v>10272</v>
       </c>
       <c r="E13">
-        <v>12939</v>
+        <v>13600</v>
       </c>
       <c r="F13">
-        <v>27883</v>
+        <v>29307</v>
       </c>
       <c r="G13">
-        <v>10770</v>
+        <v>11321</v>
       </c>
       <c r="H13">
-        <v>41742</v>
+        <v>43874</v>
       </c>
       <c r="I13">
         <v>40310</v>
@@ -8627,25 +8625,25 @@
         <v>73</v>
       </c>
       <c r="B14">
-        <v>122155</v>
+        <v>126287</v>
       </c>
       <c r="C14">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="D14">
-        <v>11167</v>
+        <v>11738</v>
       </c>
       <c r="E14">
-        <v>14792</v>
+        <v>15547</v>
       </c>
       <c r="F14">
-        <v>31863</v>
+        <v>33491</v>
       </c>
       <c r="G14">
-        <v>12308</v>
+        <v>12936</v>
       </c>
       <c r="H14">
-        <v>47703</v>
+        <v>50140</v>
       </c>
       <c r="I14">
         <v>43411</v>
@@ -8656,25 +8654,25 @@
         <v>74</v>
       </c>
       <c r="B15">
-        <v>127276</v>
+        <v>131581</v>
       </c>
       <c r="C15">
-        <v>10384</v>
+        <v>10914</v>
       </c>
       <c r="D15">
-        <v>12562</v>
+        <v>13204</v>
       </c>
       <c r="E15">
-        <v>16644</v>
+        <v>17495</v>
       </c>
       <c r="F15">
-        <v>35844</v>
+        <v>37675</v>
       </c>
       <c r="G15">
-        <v>13845</v>
+        <v>14552</v>
       </c>
       <c r="H15">
-        <v>53665</v>
+        <v>56406</v>
       </c>
       <c r="I15">
         <v>46512</v>
@@ -8685,25 +8683,25 @@
         <v>75</v>
       </c>
       <c r="B16">
-        <v>101653</v>
+        <v>105091</v>
       </c>
       <c r="C16">
-        <v>4327</v>
+        <v>4548</v>
       </c>
       <c r="D16">
-        <v>5243</v>
+        <v>5511</v>
       </c>
       <c r="E16">
-        <v>6912</v>
+        <v>7265</v>
       </c>
       <c r="F16">
-        <v>14954</v>
+        <v>15718</v>
       </c>
       <c r="G16">
-        <v>5782</v>
+        <v>6078</v>
       </c>
       <c r="H16">
-        <v>22380</v>
+        <v>23523</v>
       </c>
       <c r="I16">
         <v>31008</v>
@@ -8714,25 +8712,25 @@
         <v>76</v>
       </c>
       <c r="B17">
-        <v>106774</v>
+        <v>110385</v>
       </c>
       <c r="C17">
-        <v>5772</v>
+        <v>6067</v>
       </c>
       <c r="D17">
-        <v>6983</v>
+        <v>7340</v>
       </c>
       <c r="E17">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="F17">
-        <v>19922</v>
+        <v>20940</v>
       </c>
       <c r="G17">
-        <v>7696</v>
+        <v>8089</v>
       </c>
       <c r="H17">
-        <v>29819</v>
+        <v>31342</v>
       </c>
       <c r="I17">
         <v>34109</v>
@@ -8743,25 +8741,25 @@
         <v>12</v>
       </c>
       <c r="B18">
-        <v>111894</v>
+        <v>115679</v>
       </c>
       <c r="C18">
-        <v>7207</v>
+        <v>7576</v>
       </c>
       <c r="D18">
-        <v>8724</v>
+        <v>9170</v>
       </c>
       <c r="E18">
-        <v>11554</v>
+        <v>12145</v>
       </c>
       <c r="F18">
-        <v>24890</v>
+        <v>26162</v>
       </c>
       <c r="G18">
-        <v>9610</v>
+        <v>10101</v>
       </c>
       <c r="H18">
-        <v>37259</v>
+        <v>39162</v>
       </c>
       <c r="I18">
         <v>37210</v>
@@ -8772,25 +8770,25 @@
         <v>77</v>
       </c>
       <c r="B19">
-        <v>117035</v>
+        <v>120993</v>
       </c>
       <c r="C19">
-        <v>8653</v>
+        <v>9095</v>
       </c>
       <c r="D19">
-        <v>10465</v>
+        <v>11000</v>
       </c>
       <c r="E19">
-        <v>13875</v>
+        <v>14584</v>
       </c>
       <c r="F19">
-        <v>29960</v>
+        <v>31490</v>
       </c>
       <c r="G19">
-        <v>11524</v>
+        <v>12112</v>
       </c>
       <c r="H19">
-        <v>44698</v>
+        <v>46982</v>
       </c>
       <c r="I19">
         <v>40310</v>
@@ -8801,25 +8799,25 @@
         <v>13</v>
       </c>
       <c r="B20">
-        <v>122155</v>
+        <v>126287</v>
       </c>
       <c r="C20">
-        <v>10099</v>
+        <v>10614</v>
       </c>
       <c r="D20">
-        <v>12206</v>
+        <v>12829</v>
       </c>
       <c r="E20">
-        <v>16196</v>
+        <v>17024</v>
       </c>
       <c r="F20">
-        <v>35029</v>
+        <v>36819</v>
       </c>
       <c r="G20">
-        <v>13438</v>
+        <v>14124</v>
       </c>
       <c r="H20">
-        <v>52138</v>
+        <v>54801</v>
       </c>
       <c r="I20">
         <v>43411</v>
@@ -8830,25 +8828,25 @@
         <v>78</v>
       </c>
       <c r="B21">
-        <v>127276</v>
+        <v>131581</v>
       </c>
       <c r="C21">
-        <v>11544</v>
+        <v>12134</v>
       </c>
       <c r="D21">
-        <v>13947</v>
+        <v>14659</v>
       </c>
       <c r="E21">
-        <v>18517</v>
+        <v>19463</v>
       </c>
       <c r="F21">
-        <v>40099</v>
+        <v>42147</v>
       </c>
       <c r="G21">
-        <v>15351</v>
+        <v>16136</v>
       </c>
       <c r="H21">
-        <v>59577</v>
+        <v>62621</v>
       </c>
       <c r="I21">
         <v>46512</v>
@@ -8859,25 +8857,25 @@
         <v>14</v>
       </c>
       <c r="B22">
-        <v>132403</v>
+        <v>136881</v>
       </c>
       <c r="C22">
-        <v>12990</v>
+        <v>13653</v>
       </c>
       <c r="D22">
-        <v>15687</v>
+        <v>16489</v>
       </c>
       <c r="E22">
-        <v>20838</v>
+        <v>21903</v>
       </c>
       <c r="F22">
-        <v>45169</v>
+        <v>47476</v>
       </c>
       <c r="G22">
-        <v>17265</v>
+        <v>18147</v>
       </c>
       <c r="H22">
-        <v>67017</v>
+        <v>70440</v>
       </c>
       <c r="I22">
         <v>49613</v>
@@ -8888,25 +8886,25 @@
         <v>79</v>
       </c>
       <c r="B23">
-        <v>106774</v>
+        <v>110385</v>
       </c>
       <c r="C23">
-        <v>5192</v>
+        <v>5457</v>
       </c>
       <c r="D23">
-        <v>6291</v>
+        <v>6613</v>
       </c>
       <c r="E23">
-        <v>8297</v>
+        <v>8721</v>
       </c>
       <c r="F23">
-        <v>17947</v>
+        <v>18864</v>
       </c>
       <c r="G23">
-        <v>6943</v>
+        <v>7297</v>
       </c>
       <c r="H23">
-        <v>26863</v>
+        <v>28235</v>
       </c>
       <c r="I23">
         <v>34109</v>
@@ -8917,25 +8915,25 @@
         <v>80</v>
       </c>
       <c r="B24">
-        <v>111894</v>
+        <v>115679</v>
       </c>
       <c r="C24">
-        <v>6922</v>
+        <v>7276</v>
       </c>
       <c r="D24">
-        <v>8378</v>
+        <v>8806</v>
       </c>
       <c r="E24">
-        <v>11086</v>
+        <v>11652</v>
       </c>
       <c r="F24">
-        <v>23903</v>
+        <v>25124</v>
       </c>
       <c r="G24">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="H24">
-        <v>35781</v>
+        <v>37608</v>
       </c>
       <c r="I24">
         <v>37210</v>
@@ -8946,25 +8944,25 @@
         <v>81</v>
       </c>
       <c r="B25">
-        <v>117035</v>
+        <v>120993</v>
       </c>
       <c r="C25">
-        <v>8653</v>
+        <v>9095</v>
       </c>
       <c r="D25">
-        <v>10465</v>
+        <v>11000</v>
       </c>
       <c r="E25">
-        <v>13875</v>
+        <v>14584</v>
       </c>
       <c r="F25">
-        <v>29960</v>
+        <v>31490</v>
       </c>
       <c r="G25">
-        <v>11524</v>
+        <v>12112</v>
       </c>
       <c r="H25">
-        <v>44698</v>
+        <v>46982</v>
       </c>
       <c r="I25">
         <v>40310</v>
@@ -8975,25 +8973,25 @@
         <v>82</v>
       </c>
       <c r="B26">
-        <v>122155</v>
+        <v>126287</v>
       </c>
       <c r="C26">
-        <v>10394</v>
+        <v>10925</v>
       </c>
       <c r="D26">
-        <v>12552</v>
+        <v>13193</v>
       </c>
       <c r="E26">
-        <v>16665</v>
+        <v>17516</v>
       </c>
       <c r="F26">
-        <v>36017</v>
+        <v>37857</v>
       </c>
       <c r="G26">
-        <v>13814</v>
+        <v>14520</v>
       </c>
       <c r="H26">
-        <v>53616</v>
+        <v>56355</v>
       </c>
       <c r="I26">
         <v>43411</v>
@@ -9004,25 +9002,25 @@
         <v>83</v>
       </c>
       <c r="B27">
-        <v>127276</v>
+        <v>131581</v>
       </c>
       <c r="C27">
-        <v>12124</v>
+        <v>12744</v>
       </c>
       <c r="D27">
-        <v>14639</v>
+        <v>15387</v>
       </c>
       <c r="E27">
-        <v>19454</v>
+        <v>20448</v>
       </c>
       <c r="F27">
-        <v>42074</v>
+        <v>44223</v>
       </c>
       <c r="G27">
-        <v>16105</v>
+        <v>16927</v>
       </c>
       <c r="H27">
-        <v>62534</v>
+        <v>65728</v>
       </c>
       <c r="I27">
         <v>46512</v>
@@ -9033,25 +9031,25 @@
         <v>84</v>
       </c>
       <c r="B28">
-        <v>132403</v>
+        <v>136881</v>
       </c>
       <c r="C28">
-        <v>13855</v>
+        <v>14563</v>
       </c>
       <c r="D28">
-        <v>16726</v>
+        <v>17580</v>
       </c>
       <c r="E28">
-        <v>22243</v>
+        <v>23380</v>
       </c>
       <c r="F28">
-        <v>48131</v>
+        <v>50590</v>
       </c>
       <c r="G28">
-        <v>18395</v>
+        <v>19335</v>
       </c>
       <c r="H28">
-        <v>71451</v>
+        <v>75101</v>
       </c>
       <c r="I28">
         <v>49613</v>
@@ -9062,25 +9060,25 @@
         <v>85</v>
       </c>
       <c r="B29">
-        <v>137537</v>
+        <v>142189</v>
       </c>
       <c r="C29">
-        <v>15586</v>
+        <v>16382</v>
       </c>
       <c r="D29">
-        <v>18813</v>
+        <v>19774</v>
       </c>
       <c r="E29">
-        <v>25033</v>
+        <v>26311</v>
       </c>
       <c r="F29">
-        <v>54188</v>
+        <v>56956</v>
       </c>
       <c r="G29">
-        <v>20686</v>
+        <v>21742</v>
       </c>
       <c r="H29">
-        <v>80369</v>
+        <v>84474</v>
       </c>
       <c r="I29">
         <v>52714</v>
@@ -9091,25 +9089,25 @@
         <v>86</v>
       </c>
       <c r="B30">
-        <v>111894</v>
+        <v>115679</v>
       </c>
       <c r="C30">
-        <v>6057</v>
+        <v>6367</v>
       </c>
       <c r="D30">
-        <v>7340</v>
+        <v>7715</v>
       </c>
       <c r="E30">
-        <v>9681</v>
+        <v>10176</v>
       </c>
       <c r="F30">
-        <v>20940</v>
+        <v>22010</v>
       </c>
       <c r="G30">
-        <v>8103</v>
+        <v>8517</v>
       </c>
       <c r="H30">
-        <v>31346</v>
+        <v>32947</v>
       </c>
       <c r="I30">
         <v>37210</v>
@@ -9120,25 +9118,25 @@
         <v>123</v>
       </c>
       <c r="B31">
-        <v>122155</v>
+        <v>126287</v>
       </c>
       <c r="C31">
-        <v>10099</v>
+        <v>10614</v>
       </c>
       <c r="D31">
-        <v>12206</v>
+        <v>12829</v>
       </c>
       <c r="E31">
-        <v>16196</v>
+        <v>17024</v>
       </c>
       <c r="F31">
-        <v>35029</v>
+        <v>36819</v>
       </c>
       <c r="G31">
-        <v>13438</v>
+        <v>14124</v>
       </c>
       <c r="H31">
-        <v>52138</v>
+        <v>54801</v>
       </c>
       <c r="I31">
         <v>43411</v>
@@ -9149,25 +9147,25 @@
         <v>88</v>
       </c>
       <c r="B32">
-        <v>127276</v>
+        <v>131581</v>
       </c>
       <c r="C32">
-        <v>12124</v>
+        <v>12744</v>
       </c>
       <c r="D32">
-        <v>14639</v>
+        <v>15387</v>
       </c>
       <c r="E32">
-        <v>19454</v>
+        <v>20448</v>
       </c>
       <c r="F32">
-        <v>42074</v>
+        <v>44223</v>
       </c>
       <c r="G32">
-        <v>16105</v>
+        <v>16927</v>
       </c>
       <c r="H32">
-        <v>62534</v>
+        <v>65728</v>
       </c>
       <c r="I32">
         <v>46512</v>
@@ -9178,25 +9176,25 @@
         <v>89</v>
       </c>
       <c r="B33">
-        <v>132403</v>
+        <v>136881</v>
       </c>
       <c r="C33">
-        <v>14140</v>
+        <v>14862</v>
       </c>
       <c r="D33">
-        <v>17072</v>
+        <v>17944</v>
       </c>
       <c r="E33">
-        <v>22712</v>
+        <v>23872</v>
       </c>
       <c r="F33">
-        <v>49119</v>
+        <v>51628</v>
       </c>
       <c r="G33">
-        <v>18772</v>
+        <v>19731</v>
       </c>
       <c r="H33">
-        <v>72930</v>
+        <v>76655</v>
       </c>
       <c r="I33">
         <v>49613</v>
@@ -9207,25 +9205,25 @@
         <v>90</v>
       </c>
       <c r="B34">
-        <v>137537</v>
+        <v>142189</v>
       </c>
       <c r="C34">
-        <v>16156</v>
+        <v>16981</v>
       </c>
       <c r="D34">
-        <v>19505</v>
+        <v>20501</v>
       </c>
       <c r="E34">
-        <v>25969</v>
+        <v>27296</v>
       </c>
       <c r="F34">
-        <v>56163</v>
+        <v>59032</v>
       </c>
       <c r="G34">
-        <v>21439</v>
+        <v>22534</v>
       </c>
       <c r="H34">
-        <v>83325</v>
+        <v>87582</v>
       </c>
       <c r="I34">
         <v>52714</v>
@@ -9236,25 +9234,25 @@
         <v>19</v>
       </c>
       <c r="B35">
-        <v>142657</v>
+        <v>147482</v>
       </c>
       <c r="C35">
-        <v>18171</v>
+        <v>19100</v>
       </c>
       <c r="D35">
-        <v>21938</v>
+        <v>23059</v>
       </c>
       <c r="E35">
-        <v>29227</v>
+        <v>30720</v>
       </c>
       <c r="F35">
-        <v>63208</v>
+        <v>66436</v>
       </c>
       <c r="G35">
-        <v>24106</v>
+        <v>25338</v>
       </c>
       <c r="H35">
-        <v>93721</v>
+        <v>98508</v>
       </c>
       <c r="I35">
         <v>55814</v>
@@ -9265,25 +9263,25 @@
         <v>91</v>
       </c>
       <c r="B36">
-        <v>117035</v>
+        <v>120993</v>
       </c>
       <c r="C36">
-        <v>6922</v>
+        <v>7276</v>
       </c>
       <c r="D36">
-        <v>8388</v>
+        <v>8817</v>
       </c>
       <c r="E36">
-        <v>11066</v>
+        <v>11631</v>
       </c>
       <c r="F36">
-        <v>23933</v>
+        <v>25156</v>
       </c>
       <c r="G36">
-        <v>9264</v>
+        <v>9737</v>
       </c>
       <c r="H36">
-        <v>35830</v>
+        <v>37660</v>
       </c>
       <c r="I36">
         <v>40310</v>
@@ -9294,25 +9292,25 @@
         <v>92</v>
       </c>
       <c r="B37">
-        <v>122155</v>
+        <v>126287</v>
       </c>
       <c r="C37">
-        <v>9233</v>
+        <v>9705</v>
       </c>
       <c r="D37">
-        <v>11167</v>
+        <v>11738</v>
       </c>
       <c r="E37">
-        <v>14792</v>
+        <v>15547</v>
       </c>
       <c r="F37">
-        <v>31863</v>
+        <v>33491</v>
       </c>
       <c r="G37">
-        <v>12308</v>
+        <v>12936</v>
       </c>
       <c r="H37">
-        <v>47703</v>
+        <v>50140</v>
       </c>
       <c r="I37">
         <v>43411</v>
@@ -9323,25 +9321,25 @@
         <v>93</v>
       </c>
       <c r="B38">
-        <v>127276</v>
+        <v>131581</v>
       </c>
       <c r="C38">
-        <v>11544</v>
+        <v>12134</v>
       </c>
       <c r="D38">
-        <v>13947</v>
+        <v>14659</v>
       </c>
       <c r="E38">
-        <v>18517</v>
+        <v>19463</v>
       </c>
       <c r="F38">
-        <v>40099</v>
+        <v>42147</v>
       </c>
       <c r="G38">
-        <v>15351</v>
+        <v>16136</v>
       </c>
       <c r="H38">
-        <v>59577</v>
+        <v>62621</v>
       </c>
       <c r="I38">
         <v>46512</v>
@@ -9352,25 +9350,25 @@
         <v>94</v>
       </c>
       <c r="B39">
-        <v>132403</v>
+        <v>136881</v>
       </c>
       <c r="C39">
-        <v>13855</v>
+        <v>14563</v>
       </c>
       <c r="D39">
-        <v>16726</v>
+        <v>17580</v>
       </c>
       <c r="E39">
-        <v>22243</v>
+        <v>23380</v>
       </c>
       <c r="F39">
-        <v>48131</v>
+        <v>50590</v>
       </c>
       <c r="G39">
-        <v>18395</v>
+        <v>19335</v>
       </c>
       <c r="H39">
-        <v>71451</v>
+        <v>75101</v>
       </c>
       <c r="I39">
         <v>49613</v>
@@ -9381,25 +9379,25 @@
         <v>95</v>
       </c>
       <c r="B40">
-        <v>137537</v>
+        <v>142189</v>
       </c>
       <c r="C40">
-        <v>16156</v>
+        <v>16981</v>
       </c>
       <c r="D40">
-        <v>19505</v>
+        <v>20501</v>
       </c>
       <c r="E40">
-        <v>25969</v>
+        <v>27296</v>
       </c>
       <c r="F40">
-        <v>56163</v>
+        <v>59032</v>
       </c>
       <c r="G40">
-        <v>21439</v>
+        <v>22534</v>
       </c>
       <c r="H40">
-        <v>83325</v>
+        <v>87582</v>
       </c>
       <c r="I40">
         <v>52714</v>
@@ -9410,25 +9408,25 @@
         <v>96</v>
       </c>
       <c r="B41">
-        <v>142657</v>
+        <v>147482</v>
       </c>
       <c r="C41">
-        <v>18467</v>
+        <v>19410</v>
       </c>
       <c r="D41">
-        <v>22284</v>
+        <v>23422</v>
       </c>
       <c r="E41">
-        <v>29695</v>
+        <v>31212</v>
       </c>
       <c r="F41">
-        <v>64195</v>
+        <v>67474</v>
       </c>
       <c r="G41">
-        <v>24483</v>
+        <v>25734</v>
       </c>
       <c r="H41">
-        <v>95199</v>
+        <v>100062</v>
       </c>
       <c r="I41">
         <v>55814</v>
@@ -9439,25 +9437,25 @@
         <v>97</v>
       </c>
       <c r="B42">
-        <v>147784</v>
+        <v>152783</v>
       </c>
       <c r="C42">
-        <v>20777</v>
+        <v>21839</v>
       </c>
       <c r="D42">
-        <v>25063</v>
+        <v>26343</v>
       </c>
       <c r="E42">
-        <v>33411</v>
+        <v>35117</v>
       </c>
       <c r="F42">
-        <v>72227</v>
+        <v>75917</v>
       </c>
       <c r="G42">
-        <v>27527</v>
+        <v>28933</v>
       </c>
       <c r="H42">
-        <v>107073</v>
+        <v>112543</v>
       </c>
       <c r="I42">
         <v>58915</v>
@@ -9468,25 +9466,25 @@
         <v>98</v>
       </c>
       <c r="B43">
-        <v>122155</v>
+        <v>126287</v>
       </c>
       <c r="C43">
-        <v>7788</v>
+        <v>8186</v>
       </c>
       <c r="D43">
-        <v>9437</v>
+        <v>9919</v>
       </c>
       <c r="E43">
-        <v>12450</v>
+        <v>13086</v>
       </c>
       <c r="F43">
-        <v>26926</v>
+        <v>28302</v>
       </c>
       <c r="G43">
-        <v>10424</v>
+        <v>10957</v>
       </c>
       <c r="H43">
-        <v>40313</v>
+        <v>42372</v>
       </c>
       <c r="I43">
         <v>43411</v>
@@ -9497,25 +9495,25 @@
         <v>99</v>
       </c>
       <c r="B44">
-        <v>127276</v>
+        <v>131581</v>
       </c>
       <c r="C44">
-        <v>10384</v>
+        <v>10914</v>
       </c>
       <c r="D44">
-        <v>12562</v>
+        <v>13204</v>
       </c>
       <c r="E44">
-        <v>16644</v>
+        <v>17495</v>
       </c>
       <c r="F44">
-        <v>35844</v>
+        <v>37675</v>
       </c>
       <c r="G44">
-        <v>13845</v>
+        <v>14552</v>
       </c>
       <c r="H44">
-        <v>53665</v>
+        <v>56406</v>
       </c>
       <c r="I44">
         <v>46512</v>
@@ -9526,25 +9524,25 @@
         <v>100</v>
       </c>
       <c r="B45">
-        <v>132403</v>
+        <v>136881</v>
       </c>
       <c r="C45">
-        <v>12990</v>
+        <v>13653</v>
       </c>
       <c r="D45">
-        <v>15687</v>
+        <v>16489</v>
       </c>
       <c r="E45">
-        <v>20838</v>
+        <v>21903</v>
       </c>
       <c r="F45">
-        <v>45169</v>
+        <v>47476</v>
       </c>
       <c r="G45">
-        <v>17265</v>
+        <v>18147</v>
       </c>
       <c r="H45">
-        <v>67017</v>
+        <v>70440</v>
       </c>
       <c r="I45">
         <v>49613</v>
@@ -9555,25 +9553,25 @@
         <v>101</v>
       </c>
       <c r="B46">
-        <v>137537</v>
+        <v>142189</v>
       </c>
       <c r="C46">
-        <v>15586</v>
+        <v>16382</v>
       </c>
       <c r="D46">
-        <v>18813</v>
+        <v>19774</v>
       </c>
       <c r="E46">
-        <v>25033</v>
+        <v>26311</v>
       </c>
       <c r="F46">
-        <v>54188</v>
+        <v>56956</v>
       </c>
       <c r="G46">
-        <v>20686</v>
+        <v>21742</v>
       </c>
       <c r="H46">
-        <v>80369</v>
+        <v>84474</v>
       </c>
       <c r="I46">
         <v>52714</v>
@@ -9584,25 +9582,25 @@
         <v>102</v>
       </c>
       <c r="B47">
-        <v>142657</v>
+        <v>147482</v>
       </c>
       <c r="C47">
-        <v>18171</v>
+        <v>19100</v>
       </c>
       <c r="D47">
-        <v>21938</v>
+        <v>23059</v>
       </c>
       <c r="E47">
-        <v>29227</v>
+        <v>30720</v>
       </c>
       <c r="F47">
-        <v>63208</v>
+        <v>66436</v>
       </c>
       <c r="G47">
-        <v>24106</v>
+        <v>25338</v>
       </c>
       <c r="H47">
-        <v>93721</v>
+        <v>98508</v>
       </c>
       <c r="I47">
         <v>55814</v>
@@ -9613,25 +9611,25 @@
         <v>103</v>
       </c>
       <c r="B48">
-        <v>147784</v>
+        <v>152783</v>
       </c>
       <c r="C48">
-        <v>20777</v>
+        <v>21839</v>
       </c>
       <c r="D48">
-        <v>25063</v>
+        <v>26343</v>
       </c>
       <c r="E48">
-        <v>33411</v>
+        <v>35117</v>
       </c>
       <c r="F48">
-        <v>72227</v>
+        <v>75917</v>
       </c>
       <c r="G48">
-        <v>27527</v>
+        <v>28933</v>
       </c>
       <c r="H48">
-        <v>107073</v>
+        <v>112543</v>
       </c>
       <c r="I48">
         <v>58915</v>
@@ -9642,25 +9640,25 @@
         <v>24</v>
       </c>
       <c r="B49">
-        <v>152905</v>
+        <v>158077</v>
       </c>
       <c r="C49">
-        <v>23383</v>
+        <v>24578</v>
       </c>
       <c r="D49">
-        <v>27659</v>
+        <v>29072</v>
       </c>
       <c r="E49">
-        <v>37595</v>
+        <v>39515</v>
       </c>
       <c r="F49">
-        <v>80707</v>
+        <v>84830</v>
       </c>
       <c r="G49">
-        <v>30947</v>
+        <v>32528</v>
       </c>
       <c r="H49">
-        <v>120425</v>
+        <v>126577</v>
       </c>
       <c r="I49">
         <v>62016</v>
@@ -9671,25 +9669,25 @@
         <v>104</v>
       </c>
       <c r="B50">
-        <v>127276</v>
+        <v>131581</v>
       </c>
       <c r="C50">
-        <v>8653</v>
+        <v>9095</v>
       </c>
       <c r="D50">
-        <v>10485</v>
+        <v>11021</v>
       </c>
       <c r="E50">
-        <v>13845</v>
+        <v>14552</v>
       </c>
       <c r="F50">
-        <v>29888</v>
+        <v>31415</v>
       </c>
       <c r="G50">
-        <v>11544</v>
+        <v>12134</v>
       </c>
       <c r="H50">
-        <v>44723</v>
+        <v>47007</v>
       </c>
       <c r="I50">
         <v>46512</v>
@@ -9700,25 +9698,25 @@
         <v>105</v>
       </c>
       <c r="B51">
-        <v>132403</v>
+        <v>136881</v>
       </c>
       <c r="C51">
-        <v>11544</v>
+        <v>12134</v>
       </c>
       <c r="D51">
-        <v>13977</v>
+        <v>14691</v>
       </c>
       <c r="E51">
-        <v>18456</v>
+        <v>19399</v>
       </c>
       <c r="F51">
-        <v>39855</v>
+        <v>41891</v>
       </c>
       <c r="G51">
-        <v>15392</v>
+        <v>16178</v>
       </c>
       <c r="H51">
-        <v>59639</v>
+        <v>62685</v>
       </c>
       <c r="I51">
         <v>49613</v>
@@ -9729,25 +9727,25 @@
         <v>106</v>
       </c>
       <c r="B52">
-        <v>137537</v>
+        <v>142189</v>
       </c>
       <c r="C52">
-        <v>14435</v>
+        <v>15173</v>
       </c>
       <c r="D52">
-        <v>17479</v>
+        <v>18372</v>
       </c>
       <c r="E52">
-        <v>23068</v>
+        <v>24246</v>
       </c>
       <c r="F52">
-        <v>49821</v>
+        <v>52366</v>
       </c>
       <c r="G52">
-        <v>19240</v>
+        <v>20223</v>
       </c>
       <c r="H52">
-        <v>74554</v>
+        <v>78363</v>
       </c>
       <c r="I52">
         <v>52714</v>
@@ -9758,25 +9756,25 @@
         <v>107</v>
       </c>
       <c r="B53">
-        <v>142657</v>
+        <v>147482</v>
       </c>
       <c r="C53">
-        <v>17326</v>
+        <v>18211</v>
       </c>
       <c r="D53">
-        <v>20971</v>
+        <v>22042</v>
       </c>
       <c r="E53">
-        <v>27679</v>
+        <v>29093</v>
       </c>
       <c r="F53">
-        <v>59787</v>
+        <v>62841</v>
       </c>
       <c r="G53">
-        <v>23088</v>
+        <v>24268</v>
       </c>
       <c r="H53">
-        <v>89470</v>
+        <v>94040</v>
       </c>
       <c r="I53">
         <v>55814</v>
@@ -9787,25 +9785,25 @@
         <v>108</v>
       </c>
       <c r="B54">
-        <v>147784</v>
+        <v>152783</v>
       </c>
       <c r="C54">
-        <v>20217</v>
+        <v>21250</v>
       </c>
       <c r="D54">
-        <v>24463</v>
+        <v>25712</v>
       </c>
       <c r="E54">
-        <v>32291</v>
+        <v>33940</v>
       </c>
       <c r="F54">
-        <v>69753</v>
+        <v>73316</v>
       </c>
       <c r="G54">
-        <v>26936</v>
+        <v>28312</v>
       </c>
       <c r="H54">
-        <v>104386</v>
+        <v>109718</v>
       </c>
       <c r="I54">
         <v>58915</v>
@@ -9816,25 +9814,25 @@
         <v>109</v>
       </c>
       <c r="B55">
-        <v>152905</v>
+        <v>158077</v>
       </c>
       <c r="C55">
-        <v>23109</v>
+        <v>24289</v>
       </c>
       <c r="D55">
-        <v>27954</v>
+        <v>29382</v>
       </c>
       <c r="E55">
-        <v>36903</v>
+        <v>38788</v>
       </c>
       <c r="F55">
-        <v>79720</v>
+        <v>83792</v>
       </c>
       <c r="G55">
-        <v>30784</v>
+        <v>32357</v>
       </c>
       <c r="H55">
-        <v>119301</v>
+        <v>125395</v>
       </c>
       <c r="I55">
         <v>62016</v>
@@ -9845,25 +9843,25 @@
         <v>31</v>
       </c>
       <c r="B56">
-        <v>158046</v>
+        <v>163391</v>
       </c>
       <c r="C56">
-        <v>26000</v>
+        <v>27328</v>
       </c>
       <c r="D56">
-        <v>31446</v>
+        <v>33052</v>
       </c>
       <c r="E56">
-        <v>41514</v>
+        <v>43635</v>
       </c>
       <c r="F56">
-        <v>89686</v>
+        <v>94267</v>
       </c>
       <c r="G56">
-        <v>34632</v>
+        <v>36401</v>
       </c>
       <c r="H56">
-        <v>134217</v>
+        <v>141073</v>
       </c>
       <c r="I56">
         <v>65117</v>
@@ -9874,25 +9872,25 @@
         <v>110</v>
       </c>
       <c r="B57">
-        <v>131546</v>
+        <v>135995</v>
       </c>
       <c r="C57">
-        <v>9528</v>
+        <v>10015</v>
       </c>
       <c r="D57">
-        <v>11534</v>
+        <v>12123</v>
       </c>
       <c r="E57">
-        <v>15229</v>
+        <v>16007</v>
       </c>
       <c r="F57">
-        <v>32881</v>
+        <v>34561</v>
       </c>
       <c r="G57">
-        <v>12694</v>
+        <v>13343</v>
       </c>
       <c r="H57">
-        <v>49194</v>
+        <v>51707</v>
       </c>
       <c r="I57">
         <v>49613</v>
@@ -9903,25 +9901,25 @@
         <v>111</v>
       </c>
       <c r="B58">
-        <v>136816</v>
+        <v>141444</v>
       </c>
       <c r="C58">
-        <v>12705</v>
+        <v>13354</v>
       </c>
       <c r="D58">
-        <v>15382</v>
+        <v>16168</v>
       </c>
       <c r="E58">
-        <v>20309</v>
+        <v>21347</v>
       </c>
       <c r="F58">
-        <v>43845</v>
+        <v>46085</v>
       </c>
       <c r="G58">
-        <v>16929</v>
+        <v>17794</v>
       </c>
       <c r="H58">
-        <v>65600</v>
+        <v>68951</v>
       </c>
       <c r="I58">
         <v>52714</v>
@@ -9932,25 +9930,25 @@
         <v>112</v>
       </c>
       <c r="B59">
-        <v>142807</v>
+        <v>147637</v>
       </c>
       <c r="C59">
-        <v>15881</v>
+        <v>16692</v>
       </c>
       <c r="D59">
-        <v>19230</v>
+        <v>20212</v>
       </c>
       <c r="E59">
-        <v>25389</v>
+        <v>26686</v>
       </c>
       <c r="F59">
-        <v>54809</v>
+        <v>57609</v>
       </c>
       <c r="G59">
-        <v>21164</v>
+        <v>22245</v>
       </c>
       <c r="H59">
-        <v>82006</v>
+        <v>86195</v>
       </c>
       <c r="I59">
         <v>55814</v>
@@ -9961,25 +9959,25 @@
         <v>113</v>
       </c>
       <c r="B60">
-        <v>148838</v>
+        <v>153873</v>
       </c>
       <c r="C60">
-        <v>19057</v>
+        <v>20030</v>
       </c>
       <c r="D60">
-        <v>23078</v>
+        <v>24257</v>
       </c>
       <c r="E60">
-        <v>30469</v>
+        <v>32025</v>
       </c>
       <c r="F60">
-        <v>65773</v>
+        <v>69133</v>
       </c>
       <c r="G60">
-        <v>25399</v>
+        <v>26697</v>
       </c>
       <c r="H60">
-        <v>98412</v>
+        <v>103439</v>
       </c>
       <c r="I60">
         <v>58915</v>
@@ -9990,25 +9988,25 @@
         <v>114</v>
       </c>
       <c r="B61">
-        <v>152701</v>
+        <v>157866</v>
       </c>
       <c r="C61">
-        <v>22233</v>
+        <v>23369</v>
       </c>
       <c r="D61">
-        <v>26926</v>
+        <v>28302</v>
       </c>
       <c r="E61">
-        <v>35549</v>
+        <v>37364</v>
       </c>
       <c r="F61">
-        <v>76737</v>
+        <v>80657</v>
       </c>
       <c r="G61">
-        <v>29634</v>
+        <v>31148</v>
       </c>
       <c r="H61">
-        <v>114818</v>
+        <v>120683</v>
       </c>
       <c r="I61">
         <v>62016</v>
@@ -10019,25 +10017,25 @@
         <v>115</v>
       </c>
       <c r="B62">
-        <v>157590</v>
+        <v>162920</v>
       </c>
       <c r="C62">
-        <v>25409</v>
+        <v>26707</v>
       </c>
       <c r="D62">
-        <v>30774</v>
+        <v>32346</v>
       </c>
       <c r="E62">
-        <v>40628</v>
+        <v>42704</v>
       </c>
       <c r="F62">
-        <v>87701</v>
+        <v>92181</v>
       </c>
       <c r="G62">
-        <v>33869</v>
+        <v>35599</v>
       </c>
       <c r="H62">
-        <v>131224</v>
+        <v>137927</v>
       </c>
       <c r="I62">
         <v>65117</v>
@@ -10048,25 +10046,25 @@
         <v>35</v>
       </c>
       <c r="B63">
-        <v>163261</v>
+        <v>168783</v>
       </c>
       <c r="C63">
-        <v>28585</v>
+        <v>30046</v>
       </c>
       <c r="D63">
-        <v>34622</v>
+        <v>36391</v>
       </c>
       <c r="E63">
-        <v>45708</v>
+        <v>48043</v>
       </c>
       <c r="F63">
-        <v>98665</v>
+        <v>103704</v>
       </c>
       <c r="G63">
-        <v>38104</v>
+        <v>40050</v>
       </c>
       <c r="H63">
-        <v>147630</v>
+        <v>155171</v>
       </c>
       <c r="I63">
         <v>68218</v>
@@ -10077,25 +10075,25 @@
         <v>116</v>
       </c>
       <c r="B64">
-        <v>147786</v>
+        <v>152785</v>
       </c>
       <c r="C64">
-        <v>12124</v>
+        <v>12744</v>
       </c>
       <c r="D64">
-        <v>14680</v>
+        <v>15429</v>
       </c>
       <c r="E64">
-        <v>19383</v>
+        <v>20373</v>
       </c>
       <c r="F64">
-        <v>41850</v>
+        <v>43988</v>
       </c>
       <c r="G64">
-        <v>16166</v>
+        <v>16992</v>
       </c>
       <c r="H64">
-        <v>62619</v>
+        <v>65818</v>
       </c>
       <c r="I64">
         <v>58915</v>
@@ -10106,25 +10104,25 @@
         <v>117</v>
       </c>
       <c r="B65">
-        <v>152909</v>
+        <v>158081</v>
       </c>
       <c r="C65">
-        <v>16166</v>
+        <v>16992</v>
       </c>
       <c r="D65">
-        <v>19576</v>
+        <v>20576</v>
       </c>
       <c r="E65">
-        <v>25847</v>
+        <v>27167</v>
       </c>
       <c r="F65">
-        <v>55797</v>
+        <v>58647</v>
       </c>
       <c r="G65">
-        <v>21551</v>
+        <v>22652</v>
       </c>
       <c r="H65">
-        <v>83484</v>
+        <v>87749</v>
       </c>
       <c r="I65">
         <v>62016</v>
@@ -10135,25 +10133,25 @@
         <v>118</v>
       </c>
       <c r="B66">
-        <v>158046</v>
+        <v>163392</v>
       </c>
       <c r="C66">
-        <v>20207</v>
+        <v>21240</v>
       </c>
       <c r="D66">
-        <v>24473</v>
+        <v>25723</v>
       </c>
       <c r="E66">
-        <v>32311</v>
+        <v>33962</v>
       </c>
       <c r="F66">
-        <v>69743</v>
+        <v>73306</v>
       </c>
       <c r="G66">
-        <v>26936</v>
+        <v>28312</v>
       </c>
       <c r="H66">
-        <v>104349</v>
+        <v>109679</v>
       </c>
       <c r="I66">
         <v>65117</v>
@@ -10164,25 +10162,25 @@
         <v>119</v>
       </c>
       <c r="B67">
-        <v>163140</v>
+        <v>168658</v>
       </c>
       <c r="C67">
-        <v>24249</v>
+        <v>25487</v>
       </c>
       <c r="D67">
-        <v>29369</v>
+        <v>30870</v>
       </c>
       <c r="E67">
-        <v>38776</v>
+        <v>40756</v>
       </c>
       <c r="F67">
-        <v>83690</v>
+        <v>87965</v>
       </c>
       <c r="G67">
-        <v>32322</v>
+        <v>33973</v>
       </c>
       <c r="H67">
-        <v>125214</v>
+        <v>131610</v>
       </c>
       <c r="I67">
         <v>68218</v>
@@ -10193,25 +10191,25 @@
         <v>120</v>
       </c>
       <c r="B68">
-        <v>168292</v>
+        <v>173984</v>
       </c>
       <c r="C68">
-        <v>28290</v>
+        <v>29735</v>
       </c>
       <c r="D68">
-        <v>34266</v>
+        <v>36016</v>
       </c>
       <c r="E68">
-        <v>45240</v>
+        <v>47551</v>
       </c>
       <c r="F68">
-        <v>97636</v>
+        <v>102624</v>
       </c>
       <c r="G68">
-        <v>37707</v>
+        <v>39633</v>
       </c>
       <c r="H68">
-        <v>138383</v>
+        <v>145452</v>
       </c>
       <c r="I68">
         <v>71318</v>
@@ -10222,25 +10220,25 @@
         <v>121</v>
       </c>
       <c r="B69">
-        <v>173425</v>
+        <v>179290</v>
       </c>
       <c r="C69">
-        <v>32332</v>
+        <v>33983</v>
       </c>
       <c r="D69">
-        <v>39162</v>
+        <v>41163</v>
       </c>
       <c r="E69">
-        <v>51704</v>
+        <v>54345</v>
       </c>
       <c r="F69">
-        <v>111583</v>
+        <v>117283</v>
       </c>
       <c r="G69">
-        <v>43092</v>
+        <v>45293</v>
       </c>
       <c r="H69">
-        <v>151552</v>
+        <v>159293</v>
       </c>
       <c r="I69">
         <v>74419</v>
@@ -10251,25 +10249,25 @@
         <v>42</v>
       </c>
       <c r="B70">
-        <v>178550</v>
+        <v>184590</v>
       </c>
       <c r="C70">
-        <v>36373</v>
+        <v>38231</v>
       </c>
       <c r="D70">
-        <v>44059</v>
+        <v>46310</v>
       </c>
       <c r="E70">
-        <v>58169</v>
+        <v>61140</v>
       </c>
       <c r="F70">
-        <v>125530</v>
+        <v>131942</v>
       </c>
       <c r="G70">
-        <v>48477</v>
+        <v>50953</v>
       </c>
       <c r="H70">
-        <v>172417</v>
+        <v>181224</v>
       </c>
       <c r="I70">
         <v>77520</v>
@@ -10322,19 +10320,19 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>26974</v>
+        <v>28384</v>
       </c>
       <c r="E2">
-        <v>35525</v>
+        <v>37381</v>
       </c>
       <c r="F2">
-        <v>29689</v>
+        <v>31240</v>
       </c>
       <c r="G2">
-        <v>76872</v>
+        <v>80888</v>
       </c>
       <c r="H2">
-        <v>115033</v>
+        <v>121043</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -10348,16 +10346,16 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>26974</v>
+        <v>28384</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>29689</v>
+        <v>31240</v>
       </c>
       <c r="G3">
-        <v>76872</v>
+        <v>80888</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -10371,19 +10369,19 @@
         <v>132141</v>
       </c>
       <c r="C4">
-        <v>21083</v>
+        <v>22185</v>
       </c>
       <c r="D4">
-        <v>25562</v>
+        <v>26898</v>
       </c>
       <c r="E4">
-        <v>33651</v>
+        <v>35409</v>
       </c>
       <c r="F4">
-        <v>28125</v>
+        <v>29595</v>
       </c>
       <c r="G4">
-        <v>72827</v>
+        <v>76633</v>
       </c>
       <c r="H4">
         <v>83034</v>
@@ -10397,19 +10395,19 @@
         <v>174817</v>
       </c>
       <c r="C5">
-        <v>10542</v>
+        <v>11093</v>
       </c>
       <c r="D5">
-        <v>12781</v>
+        <v>13449</v>
       </c>
       <c r="E5">
-        <v>16825</v>
+        <v>17705</v>
       </c>
       <c r="F5">
-        <v>14062</v>
+        <v>14797</v>
       </c>
       <c r="G5">
-        <v>36414</v>
+        <v>38316</v>
       </c>
       <c r="H5">
         <v>41517</v>
@@ -10423,7 +10421,7 @@
         <v>200090</v>
       </c>
       <c r="C6">
-        <v>10542</v>
+        <v>11093</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10432,10 +10430,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>14062</v>
+        <v>14797</v>
       </c>
       <c r="G6">
-        <v>36414</v>
+        <v>38316</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -10449,19 +10447,19 @@
         <v>196156</v>
       </c>
       <c r="C7">
-        <v>5891</v>
+        <v>6199</v>
       </c>
       <c r="D7">
-        <v>7097</v>
+        <v>7468</v>
       </c>
       <c r="E7">
-        <v>9350</v>
+        <v>9838</v>
       </c>
       <c r="F7">
-        <v>7813</v>
+        <v>8222</v>
       </c>
       <c r="G7">
-        <v>20229</v>
+        <v>21286</v>
       </c>
       <c r="H7">
         <v>23064</v>
@@ -10475,7 +10473,7 @@
         <v>212945</v>
       </c>
       <c r="C8">
-        <v>5891</v>
+        <v>6199</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -10484,10 +10482,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>7813</v>
+        <v>8222</v>
       </c>
       <c r="G8">
-        <v>20229</v>
+        <v>21286</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -10527,19 +10525,19 @@
         <v>195033</v>
       </c>
       <c r="C10">
-        <v>10542</v>
+        <v>11093</v>
       </c>
       <c r="D10">
-        <v>12781</v>
+        <v>13449</v>
       </c>
       <c r="E10">
-        <v>16825</v>
+        <v>17705</v>
       </c>
       <c r="F10">
-        <v>14062</v>
+        <v>14797</v>
       </c>
       <c r="G10">
-        <v>36414</v>
+        <v>38316</v>
       </c>
       <c r="H10">
         <v>41517</v>
@@ -10553,19 +10551,19 @@
         <v>206263</v>
       </c>
       <c r="C11">
-        <v>5891</v>
+        <v>6199</v>
       </c>
       <c r="D11">
-        <v>7097</v>
+        <v>7468</v>
       </c>
       <c r="E11">
-        <v>9350</v>
+        <v>9838</v>
       </c>
       <c r="F11">
-        <v>7813</v>
+        <v>8222</v>
       </c>
       <c r="G11">
-        <v>20229</v>
+        <v>21286</v>
       </c>
       <c r="H11">
         <v>23064</v>
@@ -10579,19 +10577,19 @@
         <v>147864</v>
       </c>
       <c r="C12">
-        <v>23564</v>
+        <v>24795</v>
       </c>
       <c r="D12">
-        <v>28387</v>
+        <v>29870</v>
       </c>
       <c r="E12">
-        <v>37399</v>
+        <v>39353</v>
       </c>
       <c r="F12">
-        <v>31253</v>
+        <v>32886</v>
       </c>
       <c r="G12">
-        <v>80916</v>
+        <v>85144</v>
       </c>
       <c r="H12">
         <v>92257</v>
@@ -10605,19 +10603,19 @@
         <v>199525</v>
       </c>
       <c r="C13">
-        <v>7421</v>
+        <v>7808</v>
       </c>
       <c r="D13">
-        <v>8991</v>
+        <v>9461</v>
       </c>
       <c r="E13">
-        <v>11844</v>
+        <v>12463</v>
       </c>
       <c r="F13">
-        <v>9922</v>
+        <v>10440</v>
       </c>
       <c r="G13">
-        <v>25631</v>
+        <v>26970</v>
       </c>
       <c r="H13">
         <v>29219</v>
@@ -10631,19 +10629,19 @@
         <v>211878</v>
       </c>
       <c r="C14">
-        <v>4100</v>
+        <v>4314</v>
       </c>
       <c r="D14">
-        <v>5677</v>
+        <v>5974</v>
       </c>
       <c r="E14">
-        <v>7476</v>
+        <v>7866</v>
       </c>
       <c r="F14">
-        <v>6249</v>
+        <v>6576</v>
       </c>
       <c r="G14">
-        <v>16185</v>
+        <v>17030</v>
       </c>
       <c r="H14">
         <v>18446</v>
@@ -10657,7 +10655,7 @@
         <v>228440</v>
       </c>
       <c r="C15">
-        <v>4100</v>
+        <v>4314</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -10666,10 +10664,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>6249</v>
+        <v>6576</v>
       </c>
       <c r="G15">
-        <v>16185</v>
+        <v>17030</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -10683,19 +10681,19 @@
         <v>184924</v>
       </c>
       <c r="C16">
-        <v>16405</v>
+        <v>17262</v>
       </c>
       <c r="D16">
-        <v>21290</v>
+        <v>22403</v>
       </c>
       <c r="E16">
-        <v>28042</v>
+        <v>29508</v>
       </c>
       <c r="F16">
-        <v>23440</v>
+        <v>24665</v>
       </c>
       <c r="G16">
-        <v>60694</v>
+        <v>63865</v>
       </c>
       <c r="H16">
         <v>69199</v>
@@ -10709,19 +10707,19 @@
         <v>153479</v>
       </c>
       <c r="C17">
-        <v>16405</v>
+        <v>17262</v>
       </c>
       <c r="D17">
-        <v>21290</v>
+        <v>22403</v>
       </c>
       <c r="E17">
-        <v>28042</v>
+        <v>29508</v>
       </c>
       <c r="F17">
-        <v>23440</v>
+        <v>24665</v>
       </c>
       <c r="G17">
-        <v>60694</v>
+        <v>63865</v>
       </c>
       <c r="H17">
         <v>69199</v>
@@ -10817,16 +10815,16 @@
         <v>102798</v>
       </c>
       <c r="C2">
-        <v>18009</v>
+        <v>18923</v>
       </c>
       <c r="D2">
-        <v>77021</v>
+        <v>80927</v>
       </c>
       <c r="E2">
-        <v>19824</v>
+        <v>20829</v>
       </c>
       <c r="F2">
-        <v>51329</v>
+        <v>53933</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -10837,16 +10835,16 @@
         <v>117650</v>
       </c>
       <c r="C3">
-        <v>18009</v>
+        <v>18923</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>19824</v>
+        <v>20829</v>
       </c>
       <c r="F3">
-        <v>51329</v>
+        <v>53933</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10857,16 +10855,16 @@
         <v>127907</v>
       </c>
       <c r="C4">
-        <v>14214</v>
+        <v>14935</v>
       </c>
       <c r="D4">
-        <v>60808</v>
+        <v>63893</v>
       </c>
       <c r="E4">
-        <v>15649</v>
+        <v>16443</v>
       </c>
       <c r="F4">
-        <v>40524</v>
+        <v>42579</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -10877,16 +10875,16 @@
         <v>142870</v>
       </c>
       <c r="C5">
-        <v>14214</v>
+        <v>14935</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>15649</v>
+        <v>16443</v>
       </c>
       <c r="F5">
-        <v>40524</v>
+        <v>42579</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -10897,16 +10895,16 @@
         <v>155162</v>
       </c>
       <c r="C6">
-        <v>9481</v>
+        <v>9962</v>
       </c>
       <c r="D6">
-        <v>40539</v>
+        <v>42595</v>
       </c>
       <c r="E6">
-        <v>10433</v>
+        <v>10962</v>
       </c>
       <c r="F6">
-        <v>27014</v>
+        <v>28384</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -10917,16 +10915,16 @@
         <v>163280</v>
       </c>
       <c r="C7">
-        <v>9481</v>
+        <v>9962</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10433</v>
+        <v>10962</v>
       </c>
       <c r="F7">
-        <v>27014</v>
+        <v>28384</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -10937,16 +10935,16 @@
         <v>123578</v>
       </c>
       <c r="C8">
-        <v>23695</v>
+        <v>24897</v>
       </c>
       <c r="D8">
-        <v>101347</v>
+        <v>106488</v>
       </c>
       <c r="E8">
-        <v>26082</v>
+        <v>27405</v>
       </c>
       <c r="F8">
-        <v>67537</v>
+        <v>70963</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -10954,19 +10952,19 @@
         <v>150</v>
       </c>
       <c r="B9">
-        <v>115000</v>
+        <v>121000</v>
       </c>
       <c r="C9">
-        <v>19500</v>
+        <v>25000</v>
       </c>
       <c r="D9">
-        <v>65000</v>
+        <v>70000</v>
       </c>
       <c r="E9">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="F9">
-        <v>49000</v>
+        <v>55000</v>
       </c>
     </row>
   </sheetData>
@@ -11013,25 +11011,25 @@
         <v>125</v>
       </c>
       <c r="B2" s="1">
-        <v>262845</v>
+        <v>270864</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>26974</v>
+        <v>28384</v>
       </c>
       <c r="E2" s="1">
-        <v>35525</v>
+        <v>37381</v>
       </c>
       <c r="F2" s="1">
-        <v>29689</v>
+        <v>31240</v>
       </c>
       <c r="G2" s="1">
-        <v>76872</v>
+        <v>80888</v>
       </c>
       <c r="H2" s="1">
-        <v>115033</v>
+        <v>121043</v>
       </c>
       <c r="I2" s="1">
         <v>70560</v>
@@ -11042,22 +11040,22 @@
         <v>126</v>
       </c>
       <c r="B3" s="1">
-        <v>290723</v>
+        <v>299592</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>26974</v>
+        <v>28384</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>29689</v>
+        <v>31240</v>
       </c>
       <c r="G3" s="1">
-        <v>76872</v>
+        <v>80888</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
@@ -11071,25 +11069,25 @@
         <v>127</v>
       </c>
       <c r="B4" s="1">
-        <v>272881</v>
+        <v>281206</v>
       </c>
       <c r="C4" s="1">
-        <v>21083</v>
+        <v>22185</v>
       </c>
       <c r="D4" s="1">
-        <v>25562</v>
+        <v>26898</v>
       </c>
       <c r="E4" s="1">
-        <v>33651</v>
+        <v>35409</v>
       </c>
       <c r="F4" s="1">
-        <v>28125</v>
+        <v>29595</v>
       </c>
       <c r="G4" s="1">
-        <v>72827</v>
+        <v>76633</v>
       </c>
       <c r="H4" s="1">
-        <v>108972</v>
+        <v>114666</v>
       </c>
       <c r="I4" s="1">
         <v>90720</v>
@@ -11100,25 +11098,25 @@
         <v>128</v>
       </c>
       <c r="B5" s="1">
-        <v>323060</v>
+        <v>332916</v>
       </c>
       <c r="C5" s="1">
-        <v>10542</v>
+        <v>11093</v>
       </c>
       <c r="D5" s="1">
-        <v>12781</v>
+        <v>13449</v>
       </c>
       <c r="E5" s="1">
-        <v>16825</v>
+        <v>17705</v>
       </c>
       <c r="F5" s="1">
-        <v>14062</v>
+        <v>14797</v>
       </c>
       <c r="G5" s="1">
-        <v>36414</v>
+        <v>38316</v>
       </c>
       <c r="H5" s="1">
-        <v>54486</v>
+        <v>57333</v>
       </c>
       <c r="I5" s="1">
         <v>45360</v>
@@ -11129,10 +11127,10 @@
         <v>129</v>
       </c>
       <c r="B6" s="1">
-        <v>338672</v>
+        <v>349004</v>
       </c>
       <c r="C6" s="1">
-        <v>10542</v>
+        <v>11093</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -11141,10 +11139,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>14062</v>
+        <v>14797</v>
       </c>
       <c r="G6" s="1">
-        <v>36414</v>
+        <v>38316</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -11158,25 +11156,25 @@
         <v>130</v>
       </c>
       <c r="B7" s="1">
-        <v>339787</v>
+        <v>350153</v>
       </c>
       <c r="C7" s="1">
-        <v>5891</v>
+        <v>6199</v>
       </c>
       <c r="D7" s="1">
-        <v>7097</v>
+        <v>7468</v>
       </c>
       <c r="E7" s="1">
-        <v>9350</v>
+        <v>9838</v>
       </c>
       <c r="F7" s="1">
-        <v>7813</v>
+        <v>8222</v>
       </c>
       <c r="G7" s="1">
-        <v>20229</v>
+        <v>21286</v>
       </c>
       <c r="H7" s="1">
-        <v>30269</v>
+        <v>31851</v>
       </c>
       <c r="I7" s="1">
         <v>32760</v>
@@ -11187,10 +11185,10 @@
         <v>131</v>
       </c>
       <c r="B8" s="1">
-        <v>348708</v>
+        <v>359346</v>
       </c>
       <c r="C8" s="1">
-        <v>5891</v>
+        <v>6199</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -11199,10 +11197,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>7813</v>
+        <v>8222</v>
       </c>
       <c r="G8" s="1">
-        <v>20229</v>
+        <v>21286</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -11216,7 +11214,7 @@
         <v>132</v>
       </c>
       <c r="B9" s="1">
-        <v>363204</v>
+        <v>374285</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -11245,25 +11243,25 @@
         <v>133</v>
       </c>
       <c r="B10" s="1">
-        <v>348708</v>
+        <v>359346</v>
       </c>
       <c r="C10" s="1">
-        <v>10542</v>
+        <v>11093</v>
       </c>
       <c r="D10" s="1">
-        <v>12781</v>
+        <v>13449</v>
       </c>
       <c r="E10" s="1">
-        <v>16825</v>
+        <v>17705</v>
       </c>
       <c r="F10" s="1">
-        <v>14062</v>
+        <v>14797</v>
       </c>
       <c r="G10" s="1">
-        <v>36414</v>
+        <v>38316</v>
       </c>
       <c r="H10" s="1">
-        <v>54486</v>
+        <v>57333</v>
       </c>
       <c r="I10" s="1">
         <v>95760</v>
@@ -11274,25 +11272,25 @@
         <v>134</v>
       </c>
       <c r="B11" s="1">
-        <v>349823</v>
+        <v>360495</v>
       </c>
       <c r="C11" s="1">
-        <v>5891</v>
+        <v>6199</v>
       </c>
       <c r="D11" s="1">
-        <v>7097</v>
+        <v>7468</v>
       </c>
       <c r="E11" s="1">
-        <v>9350</v>
+        <v>9838</v>
       </c>
       <c r="F11" s="1">
-        <v>7813</v>
+        <v>8222</v>
       </c>
       <c r="G11" s="1">
-        <v>20229</v>
+        <v>21286</v>
       </c>
       <c r="H11" s="1">
-        <v>30269</v>
+        <v>31851</v>
       </c>
       <c r="I11" s="1">
         <v>57960</v>
@@ -11303,25 +11301,25 @@
         <v>135</v>
       </c>
       <c r="B12" s="1">
-        <v>292953</v>
+        <v>301890</v>
       </c>
       <c r="C12" s="1">
-        <v>23564</v>
+        <v>24795</v>
       </c>
       <c r="D12" s="1">
-        <v>28387</v>
+        <v>29870</v>
       </c>
       <c r="E12" s="1">
-        <v>37399</v>
+        <v>39353</v>
       </c>
       <c r="F12" s="1">
-        <v>31253</v>
+        <v>32886</v>
       </c>
       <c r="G12" s="1">
-        <v>80916</v>
+        <v>85144</v>
       </c>
       <c r="H12" s="1">
-        <v>121077</v>
+        <v>127403</v>
       </c>
       <c r="I12" s="1">
         <v>131040</v>
@@ -11332,25 +11330,25 @@
         <v>136</v>
       </c>
       <c r="B13" s="1">
-        <v>357629</v>
+        <v>368539</v>
       </c>
       <c r="C13" s="1">
-        <v>7421</v>
+        <v>7808</v>
       </c>
       <c r="D13" s="1">
-        <v>8991</v>
+        <v>9461</v>
       </c>
       <c r="E13" s="1">
-        <v>11844</v>
+        <v>12463</v>
       </c>
       <c r="F13" s="1">
-        <v>9922</v>
+        <v>10440</v>
       </c>
       <c r="G13" s="1">
-        <v>25631</v>
+        <v>26970</v>
       </c>
       <c r="H13" s="1">
-        <v>38347</v>
+        <v>40351</v>
       </c>
       <c r="I13" s="1">
         <v>59220</v>
@@ -11361,25 +11359,25 @@
         <v>137</v>
       </c>
       <c r="B14" s="1">
-        <v>365210</v>
+        <v>376352</v>
       </c>
       <c r="C14" s="1">
-        <v>4100</v>
+        <v>4314</v>
       </c>
       <c r="D14" s="1">
-        <v>5677</v>
+        <v>5974</v>
       </c>
       <c r="E14" s="1">
-        <v>7476</v>
+        <v>7866</v>
       </c>
       <c r="F14" s="1">
-        <v>6249</v>
+        <v>6576</v>
       </c>
       <c r="G14" s="1">
-        <v>16185</v>
+        <v>17030</v>
       </c>
       <c r="H14" s="1">
-        <v>24209</v>
+        <v>25474</v>
       </c>
       <c r="I14" s="1">
         <v>34020</v>
@@ -11390,10 +11388,10 @@
         <v>138</v>
       </c>
       <c r="B15" s="1">
-        <v>416021</v>
+        <v>428713</v>
       </c>
       <c r="C15" s="1">
-        <v>4100</v>
+        <v>4314</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -11402,10 +11400,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>6249</v>
+        <v>6576</v>
       </c>
       <c r="G15" s="1">
-        <v>16185</v>
+        <v>17030</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -11419,25 +11417,25 @@
         <v>139</v>
       </c>
       <c r="B16" s="1">
-        <v>335002</v>
+        <v>345222</v>
       </c>
       <c r="C16" s="1">
-        <v>16405</v>
+        <v>17262</v>
       </c>
       <c r="D16" s="1">
-        <v>21290</v>
+        <v>22403</v>
       </c>
       <c r="E16" s="1">
-        <v>28042</v>
+        <v>29508</v>
       </c>
       <c r="F16" s="1">
-        <v>23440</v>
+        <v>24665</v>
       </c>
       <c r="G16" s="1">
-        <v>60694</v>
+        <v>63865</v>
       </c>
       <c r="H16" s="1">
-        <v>90816</v>
+        <v>95561</v>
       </c>
       <c r="I16" s="1">
         <v>133560</v>
@@ -11448,25 +11446,25 @@
         <v>140</v>
       </c>
       <c r="B17" s="1">
-        <v>301874</v>
+        <v>311083</v>
       </c>
       <c r="C17" s="1">
-        <v>16405</v>
+        <v>17262</v>
       </c>
       <c r="D17" s="1">
-        <v>21290</v>
+        <v>22403</v>
       </c>
       <c r="E17" s="1">
-        <v>28042</v>
+        <v>29508</v>
       </c>
       <c r="F17" s="1">
-        <v>23440</v>
+        <v>24665</v>
       </c>
       <c r="G17" s="1">
-        <v>60694</v>
+        <v>63865</v>
       </c>
       <c r="H17" s="1">
-        <v>90816</v>
+        <v>95561</v>
       </c>
       <c r="I17" s="1">
         <v>57960</v>
@@ -11477,7 +11475,7 @@
         <v>151</v>
       </c>
       <c r="B18" s="1">
-        <v>391082</v>
+        <v>403013</v>
       </c>
       <c r="C18" s="1">
         <v>0</v>
@@ -11539,10 +11537,10 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>26974</v>
+        <v>28384</v>
       </c>
       <c r="E2">
-        <v>29689</v>
+        <v>31240</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -11556,10 +11554,10 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>26974</v>
+        <v>26898</v>
       </c>
       <c r="E3">
-        <v>29689</v>
+        <v>29595</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -11570,13 +11568,13 @@
         <v>140475</v>
       </c>
       <c r="C4">
-        <v>10542</v>
+        <v>11093</v>
       </c>
       <c r="D4">
-        <v>12781</v>
+        <v>13449</v>
       </c>
       <c r="E4">
-        <v>14062</v>
+        <v>14797</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -11587,13 +11585,13 @@
         <v>168040</v>
       </c>
       <c r="C5">
-        <v>10542</v>
+        <v>11093</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>14062</v>
+        <v>14797</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -11604,13 +11602,13 @@
         <v>157887</v>
       </c>
       <c r="C6">
-        <v>5891</v>
+        <v>6199</v>
       </c>
       <c r="D6">
-        <v>7097</v>
+        <v>7468</v>
       </c>
       <c r="E6">
-        <v>7813</v>
+        <v>8222</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -11621,13 +11619,13 @@
         <v>171861</v>
       </c>
       <c r="C7">
-        <v>5891</v>
+        <v>6199</v>
       </c>
       <c r="D7">
-        <v>7097</v>
+        <v>7468</v>
       </c>
       <c r="E7">
-        <v>7813</v>
+        <v>8222</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
